--- a/data/canada_trq_tracker.xlsx
+++ b/data/canada_trq_tracker.xlsx
@@ -12390,7 +12390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12471,7 +12471,12 @@
           <t>August 31 2026</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>September 7 2026</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
@@ -12524,6 +12529,9 @@
       <c r="O3" s="4" t="n">
         <v>0.3192</v>
       </c>
+      <c r="P3" s="4" t="n">
+        <v>0.3369</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12569,6 +12577,9 @@
       <c r="O4" s="4" t="n">
         <v>0.0392</v>
       </c>
+      <c r="P4" s="4" t="n">
+        <v>0.0396</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12608,6 +12619,9 @@
       <c r="O5" s="4" t="n">
         <v>0.0003</v>
       </c>
+      <c r="P5" s="4" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12664,6 +12678,10 @@
         <f>SUM(O3:O5)</f>
         <v/>
       </c>
+      <c r="P6" s="5">
+        <f>SUM(P3:P5)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12712,6 +12730,9 @@
       <c r="O7" s="4" t="n">
         <v>0.3402000000000001</v>
       </c>
+      <c r="P7" s="4" t="n">
+        <v>0.3542</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12754,6 +12775,9 @@
       <c r="O8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12775,6 +12799,9 @@
       <c r="O9" s="4" t="n">
         <v>0.3547</v>
       </c>
+      <c r="P9" s="4" t="n">
+        <v>0.3547</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12831,6 +12858,10 @@
         <f>SUM(O7:O9)</f>
         <v/>
       </c>
+      <c r="P10" s="5">
+        <f>SUM(P7:P9)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12879,6 +12910,9 @@
       <c r="O11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="P11" s="4" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12927,6 +12961,9 @@
       <c r="O12" s="4" t="n">
         <v>0.1135</v>
       </c>
+      <c r="P12" s="4" t="n">
+        <v>0.1135</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12975,6 +13012,9 @@
       <c r="O13" s="4" t="n">
         <v>0.5222</v>
       </c>
+      <c r="P13" s="4" t="n">
+        <v>0.5222</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13020,6 +13060,9 @@
       <c r="O14" s="4" t="n">
         <v>0.0008</v>
       </c>
+      <c r="P14" s="4" t="n">
+        <v>0.0008</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13065,6 +13108,9 @@
       <c r="O15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13110,6 +13156,9 @@
       <c r="O16" s="4" t="n">
         <v>0.3156</v>
       </c>
+      <c r="P16" s="4" t="n">
+        <v>0.3156</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13152,6 +13201,9 @@
       <c r="O17" s="4" t="n">
         <v>0.0128</v>
       </c>
+      <c r="P17" s="4" t="n">
+        <v>0.0406</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13194,6 +13246,9 @@
       <c r="O18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13250,6 +13305,10 @@
         <f>SUM(O11:O18)</f>
         <v/>
       </c>
+      <c r="P19" s="5">
+        <f>SUM(P11:P18)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13298,6 +13357,9 @@
       <c r="O20" s="4" t="n">
         <v>0.0027</v>
       </c>
+      <c r="P20" s="4" t="n">
+        <v>0.0027</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13346,6 +13408,9 @@
       <c r="O21" s="4" t="n">
         <v>0.2673</v>
       </c>
+      <c r="P21" s="4" t="n">
+        <v>0.2673</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13394,6 +13459,9 @@
       <c r="O22" s="4" t="n">
         <v>0.0069</v>
       </c>
+      <c r="P22" s="4" t="n">
+        <v>0.0069</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13442,6 +13510,9 @@
       <c r="O23" s="4" t="n">
         <v>0.2488</v>
       </c>
+      <c r="P23" s="4" t="n">
+        <v>0.2488</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13490,6 +13561,9 @@
       <c r="O24" s="4" t="n">
         <v>0.3697</v>
       </c>
+      <c r="P24" s="4" t="n">
+        <v>0.3697</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13538,6 +13612,9 @@
       <c r="O25" s="4" t="n">
         <v>0.0289</v>
       </c>
+      <c r="P25" s="4" t="n">
+        <v>0.0289</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13583,6 +13660,9 @@
       <c r="O26" s="4" t="n">
         <v>0.07539999999999999</v>
       </c>
+      <c r="P26" s="4" t="n">
+        <v>0.07539999999999999</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13639,6 +13719,10 @@
         <f>SUM(O20:O26)</f>
         <v/>
       </c>
+      <c r="P27" s="5">
+        <f>SUM(P20:P26)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13687,7 +13771,10 @@
       <c r="O28" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P28" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -13740,6 +13827,9 @@
       <c r="O29" s="4" t="n">
         <v>0.0037</v>
       </c>
+      <c r="P29" s="4" t="n">
+        <v>0.0037</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13788,6 +13878,9 @@
       <c r="O30" s="4" t="n">
         <v>0.2899</v>
       </c>
+      <c r="P30" s="4" t="n">
+        <v>0.2899</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13836,6 +13929,9 @@
       <c r="O31" s="4" t="n">
         <v>0.0883</v>
       </c>
+      <c r="P31" s="4" t="n">
+        <v>0.0883</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13875,6 +13971,9 @@
       <c r="O32" s="4" t="n">
         <v>0.0038</v>
       </c>
+      <c r="P32" s="4" t="n">
+        <v>0.0075</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13884,100 +13983,77 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E33" s="5">
-        <f>SUM(E28:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="5">
-        <f>SUM(F28:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="5">
-        <f>SUM(G28:G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="5">
-        <f>SUM(H28:H32)</f>
-        <v/>
-      </c>
-      <c r="I33" s="5">
-        <f>SUM(I28:I32)</f>
-        <v/>
-      </c>
-      <c r="J33" s="5">
-        <f>SUM(J28:J32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="5">
-        <f>SUM(K28:K32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="5">
-        <f>SUM(L28:L32)</f>
-        <v/>
-      </c>
-      <c r="M33" s="5">
-        <f>SUM(M28:M32)</f>
-        <v/>
-      </c>
-      <c r="N33" s="5">
-        <f>SUM(N28:N32)</f>
-        <v/>
-      </c>
-      <c r="O33" s="5">
-        <f>SUM(O28:O32)</f>
-        <v/>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>13445100</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>0.2822</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>5886100</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0.1023</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>0.1475</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>0.1559</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>0.1576</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E34" s="5">
+        <f>SUM(E28:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="5">
+        <f>SUM(F28:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="5">
+        <f>SUM(G28:G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="5">
+        <f>SUM(H28:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="5">
+        <f>SUM(I28:I33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="5">
+        <f>SUM(J28:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="5">
+        <f>SUM(K28:K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="5">
+        <f>SUM(L28:L33)</f>
+        <v/>
+      </c>
+      <c r="M34" s="5">
+        <f>SUM(M28:M33)</f>
+        <v/>
+      </c>
+      <c r="N34" s="5">
+        <f>SUM(N28:N33)</f>
+        <v/>
+      </c>
+      <c r="O34" s="5">
+        <f>SUM(O28:O33)</f>
+        <v/>
+      </c>
+      <c r="P34" s="5">
+        <f>SUM(P28:P33)</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -13988,7 +14064,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -13998,39 +14074,37 @@
         <v>0.42</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1828</v>
+        <v>0.1023</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1862</v>
+        <v>0.147</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1475</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1559</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+        <v>0.1576</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>0.1576</v>
       </c>
     </row>
     <row r="36">
@@ -14041,7 +14115,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -14051,10 +14125,10 @@
         <v>0.42</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1828</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1862</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>0.42</v>
@@ -14080,7 +14154,10 @@
       <c r="O36" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P36" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -14094,7 +14171,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -14103,32 +14180,43 @@
       <c r="D37" s="4" t="n">
         <v>0.42</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>0.42</v>
+      </c>
       <c r="F37" s="4" t="n">
-        <v>0.0009</v>
+        <v>0.42</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.0032</v>
+        <v>0.42</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -14139,88 +14227,104 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E38" s="5">
-        <f>SUM(E34:E37)</f>
-        <v/>
-      </c>
-      <c r="F38" s="5">
-        <f>SUM(F34:F37)</f>
-        <v/>
-      </c>
-      <c r="G38" s="5">
-        <f>SUM(G34:G37)</f>
-        <v/>
-      </c>
-      <c r="H38" s="5">
-        <f>SUM(H34:H37)</f>
-        <v/>
-      </c>
-      <c r="I38" s="5">
-        <f>SUM(I34:I37)</f>
-        <v/>
-      </c>
-      <c r="J38" s="5">
-        <f>SUM(J34:J37)</f>
-        <v/>
-      </c>
-      <c r="K38" s="5">
-        <f>SUM(K34:K37)</f>
-        <v/>
-      </c>
-      <c r="L38" s="5">
-        <f>SUM(L34:L37)</f>
-        <v/>
-      </c>
-      <c r="M38" s="5">
-        <f>SUM(M34:M37)</f>
-        <v/>
-      </c>
-      <c r="N38" s="5">
-        <f>SUM(N34:N37)</f>
-        <v/>
-      </c>
-      <c r="O38" s="5">
-        <f>SUM(O34:O37)</f>
-        <v/>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>5886100</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="K38" s="4" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="L38" s="4" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="M38" s="4" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0.0024</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Türkiye</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>1571700</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>0.0397</v>
-      </c>
-      <c r="K39" s="4" t="n">
-        <v>0.2893</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>0.2893</v>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>0.2893</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>0.3746</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>0.3746</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E39" s="5">
+        <f>SUM(E35:E38)</f>
+        <v/>
+      </c>
+      <c r="F39" s="5">
+        <f>SUM(F35:F38)</f>
+        <v/>
+      </c>
+      <c r="G39" s="5">
+        <f>SUM(G35:G38)</f>
+        <v/>
+      </c>
+      <c r="H39" s="5">
+        <f>SUM(H35:H38)</f>
+        <v/>
+      </c>
+      <c r="I39" s="5">
+        <f>SUM(I35:I38)</f>
+        <v/>
+      </c>
+      <c r="J39" s="5">
+        <f>SUM(J35:J38)</f>
+        <v/>
+      </c>
+      <c r="K39" s="5">
+        <f>SUM(K35:K38)</f>
+        <v/>
+      </c>
+      <c r="L39" s="5">
+        <f>SUM(L35:L38)</f>
+        <v/>
+      </c>
+      <c r="M39" s="5">
+        <f>SUM(M35:M38)</f>
+        <v/>
+      </c>
+      <c r="N39" s="5">
+        <f>SUM(N35:N38)</f>
+        <v/>
+      </c>
+      <c r="O39" s="5">
+        <f>SUM(O35:O38)</f>
+        <v/>
+      </c>
+      <c r="P39" s="5">
+        <f>SUM(P35:P38)</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -14231,7 +14335,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
@@ -14240,20 +14344,26 @@
       <c r="D40" s="4" t="n">
         <v>0.45</v>
       </c>
+      <c r="I40" s="4" t="n">
+        <v>0.0397</v>
+      </c>
       <c r="K40" s="4" t="n">
-        <v>0.0924</v>
+        <v>0.2893</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.1692</v>
+        <v>0.2893</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.1692</v>
+        <v>0.2893</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.2455</v>
+        <v>0.3746</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.2455</v>
+        <v>0.3746</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0.3746</v>
       </c>
     </row>
     <row r="41">
@@ -14264,100 +14374,97 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E41" s="5">
-        <f>SUM(E39:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="5">
-        <f>SUM(F39:F40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="5">
-        <f>SUM(G39:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="5">
-        <f>SUM(H39:H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="5">
-        <f>SUM(I39:I40)</f>
-        <v/>
-      </c>
-      <c r="J41" s="5">
-        <f>SUM(J39:J40)</f>
-        <v/>
-      </c>
-      <c r="K41" s="5">
-        <f>SUM(K39:K40)</f>
-        <v/>
-      </c>
-      <c r="L41" s="5">
-        <f>SUM(L39:L40)</f>
-        <v/>
-      </c>
-      <c r="M41" s="5">
-        <f>SUM(M39:M40)</f>
-        <v/>
-      </c>
-      <c r="N41" s="5">
-        <f>SUM(N39:N40)</f>
-        <v/>
-      </c>
-      <c r="O41" s="5">
-        <f>SUM(O39:O40)</f>
-        <v/>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1571700</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>0.0924</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>3753500</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="N42" s="4" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="O42" s="4" t="n">
-        <v>0.0146</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E42" s="5">
+        <f>SUM(E40:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="5">
+        <f>SUM(F40:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>SUM(G40:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="5">
+        <f>SUM(H40:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="5">
+        <f>SUM(I40:I41)</f>
+        <v/>
+      </c>
+      <c r="J42" s="5">
+        <f>SUM(J40:J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="5">
+        <f>SUM(K40:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="5">
+        <f>SUM(L40:L41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="5">
+        <f>SUM(M40:M41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="5">
+        <f>SUM(N40:N41)</f>
+        <v/>
+      </c>
+      <c r="O42" s="5">
+        <f>SUM(O40:O41)</f>
+        <v/>
+      </c>
+      <c r="P42" s="5">
+        <f>SUM(P40:P41)</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -14368,7 +14475,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -14378,34 +14485,37 @@
         <v>0.52</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.1828</v>
+        <v>0.0218</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.1828</v>
+        <v>0.0218</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.1828</v>
+        <v>0.0218</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.1983</v>
+        <v>0.0218</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>0.1993</v>
+        <v>0.0218</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.1993</v>
+        <v>0.0146</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.1993</v>
+        <v>0.0146</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>0.2009</v>
+        <v>0.0146</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.2009</v>
+        <v>0.0146</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0.2009</v>
+        <v>0.0146</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0.0146</v>
       </c>
     </row>
     <row r="44">
@@ -14416,7 +14526,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
@@ -14426,34 +14536,37 @@
         <v>0.52</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.1828</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.1828</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.1828</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.1983</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.1993</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.1993</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.1993</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.2009</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.2009</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.2009</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0.2065</v>
       </c>
     </row>
     <row r="45">
@@ -14464,7 +14577,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -14474,34 +14587,37 @@
         <v>0.52</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.3483</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>0.3483</v>
       </c>
     </row>
     <row r="46">
@@ -14512,51 +14628,106 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3753500</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E46" s="5">
-        <f>SUM(E42:E45)</f>
-        <v/>
-      </c>
-      <c r="F46" s="5">
-        <f>SUM(F42:F45)</f>
-        <v/>
-      </c>
-      <c r="G46" s="5">
-        <f>SUM(G42:G45)</f>
-        <v/>
-      </c>
-      <c r="H46" s="5">
-        <f>SUM(H42:H45)</f>
-        <v/>
-      </c>
-      <c r="I46" s="5">
-        <f>SUM(I42:I45)</f>
-        <v/>
-      </c>
-      <c r="J46" s="5">
-        <f>SUM(J42:J45)</f>
-        <v/>
-      </c>
-      <c r="K46" s="5">
-        <f>SUM(K42:K45)</f>
-        <v/>
-      </c>
-      <c r="L46" s="5">
-        <f>SUM(L42:L45)</f>
-        <v/>
-      </c>
-      <c r="M46" s="5">
-        <f>SUM(M42:M45)</f>
-        <v/>
-      </c>
-      <c r="N46" s="5">
-        <f>SUM(N42:N45)</f>
-        <v/>
-      </c>
-      <c r="O46" s="5">
-        <f>SUM(O42:O45)</f>
+      <c r="E47" s="5">
+        <f>SUM(E43:E46)</f>
+        <v/>
+      </c>
+      <c r="F47" s="5">
+        <f>SUM(F43:F46)</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>SUM(G43:G46)</f>
+        <v/>
+      </c>
+      <c r="H47" s="5">
+        <f>SUM(H43:H46)</f>
+        <v/>
+      </c>
+      <c r="I47" s="5">
+        <f>SUM(I43:I46)</f>
+        <v/>
+      </c>
+      <c r="J47" s="5">
+        <f>SUM(J43:J46)</f>
+        <v/>
+      </c>
+      <c r="K47" s="5">
+        <f>SUM(K43:K46)</f>
+        <v/>
+      </c>
+      <c r="L47" s="5">
+        <f>SUM(L43:L46)</f>
+        <v/>
+      </c>
+      <c r="M47" s="5">
+        <f>SUM(M43:M46)</f>
+        <v/>
+      </c>
+      <c r="N47" s="5">
+        <f>SUM(N43:N46)</f>
+        <v/>
+      </c>
+      <c r="O47" s="5">
+        <f>SUM(O43:O46)</f>
+        <v/>
+      </c>
+      <c r="P47" s="5">
+        <f>SUM(P43:P46)</f>
         <v/>
       </c>
     </row>
@@ -14571,7 +14742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14652,7 +14823,12 @@
           <t>August 31 2026</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>September 7 2026</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
@@ -14705,6 +14881,9 @@
       <c r="O3" s="4" t="n">
         <v>0.3165</v>
       </c>
+      <c r="P3" s="4" t="n">
+        <v>0.3165</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14753,6 +14932,9 @@
       <c r="O4" s="4" t="n">
         <v>0.6835</v>
       </c>
+      <c r="P4" s="4" t="n">
+        <v>0.6835</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14809,6 +14991,10 @@
         <f>SUM(O3:O4)</f>
         <v/>
       </c>
+      <c r="P5" s="5">
+        <f>SUM(P3:P4)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14857,6 +15043,9 @@
       <c r="O6" s="4" t="n">
         <v>0.0452</v>
       </c>
+      <c r="P6" s="4" t="n">
+        <v>0.0452</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14905,6 +15094,9 @@
       <c r="O7" s="4" t="n">
         <v>0.0261</v>
       </c>
+      <c r="P7" s="4" t="n">
+        <v>0.0261</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14953,6 +15145,9 @@
       <c r="O8" s="4" t="n">
         <v>0.0009</v>
       </c>
+      <c r="P8" s="4" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15001,6 +15196,9 @@
       <c r="O9" s="4" t="n">
         <v>0.0142</v>
       </c>
+      <c r="P9" s="4" t="n">
+        <v>0.0142</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15049,6 +15247,9 @@
       <c r="O10" s="4" t="n">
         <v>0.2225</v>
       </c>
+      <c r="P10" s="4" t="n">
+        <v>0.2225</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15097,6 +15298,9 @@
       <c r="O11" s="4" t="n">
         <v>0.2087</v>
       </c>
+      <c r="P11" s="4" t="n">
+        <v>0.2087</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15145,6 +15349,9 @@
       <c r="O12" s="4" t="n">
         <v>0.08310000000000001</v>
       </c>
+      <c r="P12" s="4" t="n">
+        <v>0.08310000000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15193,6 +15400,14 @@
       <c r="O13" s="4" t="n">
         <v>0.3239</v>
       </c>
+      <c r="P13" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15241,6 +15456,9 @@
       <c r="O14" s="4" t="n">
         <v>0.001</v>
       </c>
+      <c r="P14" s="4" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15289,6 +15507,9 @@
       <c r="O15" s="4" t="n">
         <v>0.0624</v>
       </c>
+      <c r="P15" s="4" t="n">
+        <v>0.0624</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15334,6 +15555,9 @@
       <c r="O16" s="4" t="n">
         <v>0.0013</v>
       </c>
+      <c r="P16" s="4" t="n">
+        <v>0.0013</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15390,6 +15614,10 @@
         <f>SUM(O6:O16)</f>
         <v/>
       </c>
+      <c r="P17" s="5">
+        <f>SUM(P6:P16)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15438,6 +15666,9 @@
       <c r="O18" s="4" t="n">
         <v>0.0276</v>
       </c>
+      <c r="P18" s="4" t="n">
+        <v>0.0276</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15486,6 +15717,9 @@
       <c r="O19" s="4" t="n">
         <v>0.2081</v>
       </c>
+      <c r="P19" s="4" t="n">
+        <v>0.2098</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15534,6 +15768,9 @@
       <c r="O20" s="4" t="n">
         <v>0.0175</v>
       </c>
+      <c r="P20" s="4" t="n">
+        <v>0.0175</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15579,6 +15816,9 @@
       <c r="O21" s="4" t="n">
         <v>0.3302</v>
       </c>
+      <c r="P21" s="4" t="n">
+        <v>0.3302</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15609,6 +15849,9 @@
       <c r="O22" s="4" t="n">
         <v>0.0043</v>
       </c>
+      <c r="P22" s="4" t="n">
+        <v>0.0043</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15633,6 +15876,9 @@
       <c r="O23" s="4" t="n">
         <v>0.0086</v>
       </c>
+      <c r="P23" s="4" t="n">
+        <v>0.0086</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15642,100 +15888,77 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E24" s="5">
-        <f>SUM(E18:E23)</f>
-        <v/>
-      </c>
-      <c r="F24" s="5">
-        <f>SUM(F18:F23)</f>
-        <v/>
-      </c>
-      <c r="G24" s="5">
-        <f>SUM(G18:G23)</f>
-        <v/>
-      </c>
-      <c r="H24" s="5">
-        <f>SUM(H18:H23)</f>
-        <v/>
-      </c>
-      <c r="I24" s="5">
-        <f>SUM(I18:I23)</f>
-        <v/>
-      </c>
-      <c r="J24" s="5">
-        <f>SUM(J18:J23)</f>
-        <v/>
-      </c>
-      <c r="K24" s="5">
-        <f>SUM(K18:K23)</f>
-        <v/>
-      </c>
-      <c r="L24" s="5">
-        <f>SUM(L18:L23)</f>
-        <v/>
-      </c>
-      <c r="M24" s="5">
-        <f>SUM(M18:M23)</f>
-        <v/>
-      </c>
-      <c r="N24" s="5">
-        <f>SUM(N18:N23)</f>
-        <v/>
-      </c>
-      <c r="O24" s="5">
-        <f>SUM(O18:O23)</f>
-        <v/>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2785800</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Coated Steel Sheet</t>
+          <t>Cold-Rolled Sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>31128200</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>0.0304</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>0.2387</v>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>0.2387</v>
-      </c>
-      <c r="O25" s="4" t="n">
-        <v>0.2462</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E25" s="5">
+        <f>SUM(E18:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="5">
+        <f>SUM(F18:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="5">
+        <f>SUM(G18:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="5">
+        <f>SUM(H18:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="5">
+        <f>SUM(I18:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="5">
+        <f>SUM(J18:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="5">
+        <f>SUM(K18:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="5">
+        <f>SUM(L18:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="5">
+        <f>SUM(M18:M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="5">
+        <f>SUM(N18:N24)</f>
+        <v/>
+      </c>
+      <c r="O25" s="5">
+        <f>SUM(O18:O24)</f>
+        <v/>
+      </c>
+      <c r="P25" s="5">
+        <f>SUM(P18:P24)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -15746,7 +15969,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -15756,34 +15979,37 @@
         <v>0.25</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.0003</v>
+        <v>0.0304</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.0609</v>
+        <v>0.0304</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.0617</v>
+        <v>0.0304</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.0616</v>
+        <v>0.0304</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.0793</v>
+        <v>0.0304</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.0793</v>
+        <v>0.0304</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0793</v>
+        <v>0.0304</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0795</v>
+        <v>0.2387</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.0795</v>
+        <v>0.2387</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.0795</v>
+        <v>0.2462</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0.2462</v>
       </c>
     </row>
     <row r="27">
@@ -15794,7 +16020,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
@@ -15804,39 +16030,37 @@
         <v>0.25</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0609</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2141</v>
+        <v>0.0617</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.25</v>
+        <v>0.0616</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.25</v>
+        <v>0.0793</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.25</v>
+        <v>0.0793</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.25</v>
+        <v>0.0793</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.25</v>
+        <v>0.0795</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.25</v>
+        <v>0.0795</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+        <v>0.0795</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0.0911</v>
       </c>
     </row>
     <row r="28">
@@ -15847,7 +16071,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
@@ -15857,34 +16081,42 @@
         <v>0.25</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.0382</v>
+        <v>0.0001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.0382</v>
+        <v>0.0001</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.0447</v>
+        <v>0.2141</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0447</v>
+        <v>0.25</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.0447</v>
+        <v>0.25</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.25</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.25</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.25</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.0483</v>
+        <v>0.25</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.0483</v>
+        <v>0.25</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -15895,7 +16127,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
@@ -15905,34 +16137,37 @@
         <v>0.25</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0</v>
+        <v>0.0382</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.0341</v>
+        <v>0.0382</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0447</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.0372</v>
+        <v>0.0447</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.039</v>
+        <v>0.0447</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.039</v>
+        <v>0.0482</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.039</v>
+        <v>0.0482</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0482</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.0489</v>
+        <v>0.0483</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.0487</v>
+        <v>0.0483</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>0.04940000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -15943,7 +16178,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -15953,34 +16188,37 @@
         <v>0.25</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0341</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0372</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.0372</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.039</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.039</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.039</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.0294</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.0294</v>
+        <v>0.0489</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.0294</v>
+        <v>0.0487</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0.0533</v>
       </c>
     </row>
     <row r="31">
@@ -15991,7 +16229,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -16000,32 +16238,38 @@
       <c r="D31" s="4" t="n">
         <v>0.25</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>0.0213</v>
+      </c>
       <c r="F31" s="4" t="n">
-        <v>0.0451</v>
+        <v>0.0213</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.0454</v>
+        <v>0.0213</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0454</v>
+        <v>0.0213</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.0454</v>
+        <v>0.0213</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.096</v>
+        <v>0.0256</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.0256</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.0294</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1044</v>
+        <v>0.0294</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1044</v>
+        <v>0.0294</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>0.0294</v>
       </c>
     </row>
     <row r="32">
@@ -16036,7 +16280,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -16046,31 +16290,34 @@
         <v>0.25</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.0451</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.0454</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.0454</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.0152</v>
+        <v>0.0454</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.096</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.1027</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.1027</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.1044</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.0197</v>
+        <v>0.1044</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>0.1044</v>
       </c>
     </row>
     <row r="33">
@@ -16081,7 +16328,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -16091,31 +16338,34 @@
         <v>0.25</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.0195</v>
+        <v>0.0146</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.021</v>
+        <v>0.0146</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.021</v>
+        <v>0.0146</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.021</v>
+        <v>0.0152</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.0369</v>
+        <v>0.0157</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.0369</v>
+        <v>0.0157</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.0369</v>
+        <v>0.0157</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.0369</v>
+        <v>0.0157</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.0369</v>
+        <v>0.0197</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>0.0226</v>
       </c>
     </row>
     <row r="34">
@@ -16126,7 +16376,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
@@ -16135,29 +16385,35 @@
       <c r="D34" s="4" t="n">
         <v>0.25</v>
       </c>
+      <c r="F34" s="4" t="n">
+        <v>0.0195</v>
+      </c>
       <c r="G34" s="4" t="n">
-        <v>0.0014</v>
+        <v>0.021</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.0014</v>
+        <v>0.021</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.0014</v>
+        <v>0.021</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.0014</v>
+        <v>0.0369</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.0014</v>
+        <v>0.0369</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.0014</v>
+        <v>0.0369</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.0014</v>
+        <v>0.0369</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.0014</v>
+        <v>0.0369</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>0.0369</v>
       </c>
     </row>
     <row r="35">
@@ -16168,7 +16424,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
@@ -16177,20 +16433,32 @@
       <c r="D35" s="4" t="n">
         <v>0.25</v>
       </c>
+      <c r="G35" s="4" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0.0014</v>
+      </c>
       <c r="K35" s="4" t="n">
-        <v>0.0063</v>
+        <v>0.0014</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.0063</v>
+        <v>0.0014</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.0063</v>
+        <v>0.0014</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.0063</v>
+        <v>0.0014</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.0063</v>
+        <v>0.0014</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>0.0014</v>
       </c>
     </row>
     <row r="36">
@@ -16201,7 +16469,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -16210,11 +16478,23 @@
       <c r="D36" s="4" t="n">
         <v>0.25</v>
       </c>
+      <c r="K36" s="4" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>0.0063</v>
+      </c>
       <c r="N36" s="4" t="n">
-        <v>0.0027</v>
+        <v>0.0063</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.0027</v>
+        <v>0.0063</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0.0063</v>
       </c>
     </row>
     <row r="37">
@@ -16225,7 +16505,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -16235,10 +16515,13 @@
         <v>0.25</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.0002</v>
+        <v>0.0027</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0.0002</v>
+        <v>0.0027</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="38">
@@ -16249,7 +16532,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -16258,8 +16541,14 @@
       <c r="D38" s="4" t="n">
         <v>0.25</v>
       </c>
+      <c r="N38" s="4" t="n">
+        <v>0.0002</v>
+      </c>
       <c r="O38" s="4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0002</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>0.0002</v>
       </c>
     </row>
     <row r="39">
@@ -16270,100 +16559,80 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E39" s="5">
-        <f>SUM(E25:E38)</f>
-        <v/>
-      </c>
-      <c r="F39" s="5">
-        <f>SUM(F25:F38)</f>
-        <v/>
-      </c>
-      <c r="G39" s="5">
-        <f>SUM(G25:G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="5">
-        <f>SUM(H25:H38)</f>
-        <v/>
-      </c>
-      <c r="I39" s="5">
-        <f>SUM(I25:I38)</f>
-        <v/>
-      </c>
-      <c r="J39" s="5">
-        <f>SUM(J25:J38)</f>
-        <v/>
-      </c>
-      <c r="K39" s="5">
-        <f>SUM(K25:K38)</f>
-        <v/>
-      </c>
-      <c r="L39" s="5">
-        <f>SUM(L25:L38)</f>
-        <v/>
-      </c>
-      <c r="M39" s="5">
-        <f>SUM(M25:M38)</f>
-        <v/>
-      </c>
-      <c r="N39" s="5">
-        <f>SUM(N25:N38)</f>
-        <v/>
-      </c>
-      <c r="O39" s="5">
-        <f>SUM(O25:O38)</f>
-        <v/>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>31128200</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Coated Steel Sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>28710400</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0.0832</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>0.0832</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0.0832</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>0.0832</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>0.08349999999999999</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>0.08349999999999999</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>0.08349999999999999</v>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>0.08349999999999999</v>
-      </c>
-      <c r="N40" s="4" t="n">
-        <v>0.08349999999999999</v>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v>0.2142</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E40" s="5">
+        <f>SUM(E26:E39)</f>
+        <v/>
+      </c>
+      <c r="F40" s="5">
+        <f>SUM(F26:F39)</f>
+        <v/>
+      </c>
+      <c r="G40" s="5">
+        <f>SUM(G26:G39)</f>
+        <v/>
+      </c>
+      <c r="H40" s="5">
+        <f>SUM(H26:H39)</f>
+        <v/>
+      </c>
+      <c r="I40" s="5">
+        <f>SUM(I26:I39)</f>
+        <v/>
+      </c>
+      <c r="J40" s="5">
+        <f>SUM(J26:J39)</f>
+        <v/>
+      </c>
+      <c r="K40" s="5">
+        <f>SUM(K26:K39)</f>
+        <v/>
+      </c>
+      <c r="L40" s="5">
+        <f>SUM(L26:L39)</f>
+        <v/>
+      </c>
+      <c r="M40" s="5">
+        <f>SUM(M26:M39)</f>
+        <v/>
+      </c>
+      <c r="N40" s="5">
+        <f>SUM(N26:N39)</f>
+        <v/>
+      </c>
+      <c r="O40" s="5">
+        <f>SUM(O26:O39)</f>
+        <v/>
+      </c>
+      <c r="P40" s="5">
+        <f>SUM(P26:P39)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -16374,7 +16643,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
@@ -16384,34 +16653,37 @@
         <v>0.45</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.0832</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.0832</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.0832</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.0832</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>0.3459</v>
+        <v>0.2142</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>0.2142</v>
       </c>
     </row>
     <row r="42">
@@ -16422,7 +16694,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
@@ -16431,32 +16703,38 @@
       <c r="D42" s="4" t="n">
         <v>0.45</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>0.3459</v>
+      </c>
       <c r="F42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.3459</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0.3459</v>
       </c>
     </row>
     <row r="43">
@@ -16467,7 +16745,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
@@ -16476,20 +16754,35 @@
       <c r="D43" s="4" t="n">
         <v>0.45</v>
       </c>
+      <c r="F43" s="4" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
       <c r="K43" s="4" t="n">
-        <v>0.4389</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.4389</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>0.4389</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.4389</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0.4389</v>
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0.0007000000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -16500,148 +16793,113 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E44" s="5">
-        <f>SUM(E40:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="5">
-        <f>SUM(F40:F43)</f>
-        <v/>
-      </c>
-      <c r="G44" s="5">
-        <f>SUM(G40:G43)</f>
-        <v/>
-      </c>
-      <c r="H44" s="5">
-        <f>SUM(H40:H43)</f>
-        <v/>
-      </c>
-      <c r="I44" s="5">
-        <f>SUM(I40:I43)</f>
-        <v/>
-      </c>
-      <c r="J44" s="5">
-        <f>SUM(J40:J43)</f>
-        <v/>
-      </c>
-      <c r="K44" s="5">
-        <f>SUM(K40:K43)</f>
-        <v/>
-      </c>
-      <c r="L44" s="5">
-        <f>SUM(L40:L43)</f>
-        <v/>
-      </c>
-      <c r="M44" s="5">
-        <f>SUM(M40:M43)</f>
-        <v/>
-      </c>
-      <c r="N44" s="5">
-        <f>SUM(N40:N43)</f>
-        <v/>
-      </c>
-      <c r="O44" s="5">
-        <f>SUM(O40:O43)</f>
-        <v/>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>28710400</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0.4389</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>8750300</v>
+        <v>28710400</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v>0.0025</v>
+        <v>0.45</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>0.0003</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>8750300</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0.2277</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>0.2285</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>0.2297</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>0.2419</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>0.2441</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>0.2444</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>0.4215</v>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>0.4215</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>0.4215</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>0.4215</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E46" s="5">
+        <f>SUM(E41:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="5">
+        <f>SUM(F41:F45)</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>SUM(G41:G45)</f>
+        <v/>
+      </c>
+      <c r="H46" s="5">
+        <f>SUM(H41:H45)</f>
+        <v/>
+      </c>
+      <c r="I46" s="5">
+        <f>SUM(I41:I45)</f>
+        <v/>
+      </c>
+      <c r="J46" s="5">
+        <f>SUM(J41:J45)</f>
+        <v/>
+      </c>
+      <c r="K46" s="5">
+        <f>SUM(K41:K45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="5">
+        <f>SUM(L41:L45)</f>
+        <v/>
+      </c>
+      <c r="M46" s="5">
+        <f>SUM(M41:M45)</f>
+        <v/>
+      </c>
+      <c r="N46" s="5">
+        <f>SUM(N41:N45)</f>
+        <v/>
+      </c>
+      <c r="O46" s="5">
+        <f>SUM(O41:O45)</f>
+        <v/>
+      </c>
+      <c r="P46" s="5">
+        <f>SUM(P41:P45)</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -16652,7 +16910,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
@@ -16662,34 +16920,37 @@
         <v>0.58</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.1228</v>
+        <v>0.0025</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.1253</v>
+        <v>0.0025</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>0.1543</v>
+        <v>0.0025</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.1545</v>
+        <v>0.0025</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>0.1549</v>
+        <v>0.0025</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0.155</v>
+        <v>0.0025</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.1712</v>
+        <v>0.0025</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>0.1712</v>
+        <v>0.0025</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.1712</v>
+        <v>0.0025</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>0.1712</v>
+        <v>0.0025</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>0.0025</v>
       </c>
     </row>
     <row r="48">
@@ -16700,7 +16961,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C48" s="3" t="n">
@@ -16710,34 +16971,37 @@
         <v>0.58</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.0019</v>
+        <v>0.2277</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.0019</v>
+        <v>0.2285</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>0.0035</v>
+        <v>0.2297</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0035</v>
+        <v>0.2419</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>0.0035</v>
+        <v>0.2441</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0.016</v>
+        <v>0.2444</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.016</v>
+        <v>0.4215</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.016</v>
+        <v>0.4215</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.016</v>
+        <v>0.4215</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0.016</v>
+        <v>0.4215</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0.4215</v>
       </c>
     </row>
     <row r="49">
@@ -16748,7 +17012,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C49" s="3" t="n">
@@ -16758,34 +17022,37 @@
         <v>0.58</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.0068</v>
+        <v>0.1228</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.0095</v>
+        <v>0.1253</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>0.01</v>
+        <v>0.1543</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.0104</v>
+        <v>0.1545</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>0.0105</v>
+        <v>0.1549</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0.0133</v>
+        <v>0.155</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>0.0133</v>
+        <v>0.1712</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>0.0133</v>
+        <v>0.1712</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.0133</v>
+        <v>0.1712</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>0.0133</v>
+        <v>0.1712</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>0.1712</v>
       </c>
     </row>
     <row r="50">
@@ -16796,7 +17063,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
@@ -16806,34 +17073,37 @@
         <v>0.58</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.0191</v>
+        <v>0.0019</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.0236</v>
+        <v>0.0019</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>0.0294</v>
+        <v>0.0035</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>0.0546</v>
+        <v>0.0035</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.016</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.016</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.016</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.016</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.016</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="51">
@@ -16844,7 +17114,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
@@ -16853,32 +17123,38 @@
       <c r="D51" s="4" t="n">
         <v>0.58</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>0.0068</v>
+      </c>
       <c r="F51" s="4" t="n">
-        <v>0.0017</v>
+        <v>0.0095</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>0.0028</v>
+        <v>0.01</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0104</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>0.0066</v>
+        <v>0.0105</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0.0066</v>
+        <v>0.0133</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>0.0072</v>
+        <v>0.0133</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>0.0072</v>
+        <v>0.0133</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.0072</v>
+        <v>0.0133</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>0.0072</v>
+        <v>0.0133</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>0.0133</v>
       </c>
     </row>
     <row r="52">
@@ -16889,7 +17165,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
@@ -16898,32 +17174,38 @@
       <c r="D52" s="4" t="n">
         <v>0.58</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>0.0191</v>
+      </c>
       <c r="F52" s="4" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0236</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0294</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.1435</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>0.2085</v>
+        <v>0.0546</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.29</v>
+        <v>0.0708</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.2946</v>
+        <v>0.0708</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.2946</v>
+        <v>0.0708</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.2923</v>
+        <v>0.0708</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.2923</v>
+        <v>0.0708</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>0.0708</v>
       </c>
     </row>
     <row r="53">
@@ -16934,7 +17216,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
@@ -16943,29 +17225,35 @@
       <c r="D53" s="4" t="n">
         <v>0.58</v>
       </c>
+      <c r="F53" s="4" t="n">
+        <v>0.0017</v>
+      </c>
       <c r="G53" s="4" t="n">
-        <v>0.0005</v>
+        <v>0.0028</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0066</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0066</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0072</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0072</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0072</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>0.0001</v>
+        <v>0.0072</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0.0072</v>
       </c>
     </row>
     <row r="54">
@@ -16976,7 +17264,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
@@ -16985,29 +17273,35 @@
       <c r="D54" s="4" t="n">
         <v>0.58</v>
       </c>
+      <c r="F54" s="4" t="n">
+        <v>0.008500000000000001</v>
+      </c>
       <c r="G54" s="4" t="n">
-        <v>0</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0</v>
+        <v>0.1435</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>0</v>
+        <v>0.2085</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0</v>
+        <v>0.2946</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0</v>
+        <v>0.2946</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0</v>
+        <v>0.2923</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0</v>
+        <v>0.2923</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0.2923</v>
       </c>
     </row>
     <row r="55">
@@ -17018,7 +17312,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C55" s="3" t="n">
@@ -17028,28 +17322,31 @@
         <v>0.58</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0005</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0001</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>0.0001</v>
       </c>
     </row>
     <row r="56">
@@ -17060,7 +17357,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
@@ -17070,28 +17367,31 @@
         <v>0.58</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.0004</v>
+        <v>0</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -17102,7 +17402,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
@@ -17112,28 +17412,31 @@
         <v>0.58</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>0</v>
+        <v>0.0022</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>0.0022</v>
       </c>
     </row>
     <row r="58">
@@ -17144,7 +17447,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C58" s="3" t="n">
@@ -17153,26 +17456,32 @@
       <c r="D58" s="4" t="n">
         <v>0.58</v>
       </c>
+      <c r="G58" s="4" t="n">
+        <v>0.0004</v>
+      </c>
       <c r="H58" s="4" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0</v>
+        <v>0.0004</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0.0004</v>
       </c>
     </row>
     <row r="59">
@@ -17183,7 +17492,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
@@ -17192,6 +17501,9 @@
       <c r="D59" s="4" t="n">
         <v>0.58</v>
       </c>
+      <c r="G59" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="H59" s="4" t="n">
         <v>0</v>
       </c>
@@ -17213,6 +17525,9 @@
       <c r="O59" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="P59" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17222,7 +17537,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
@@ -17231,6 +17546,9 @@
       <c r="D60" s="4" t="n">
         <v>0.58</v>
       </c>
+      <c r="H60" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="I60" s="4" t="n">
         <v>0</v>
       </c>
@@ -17249,6 +17567,9 @@
       <c r="O60" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="P60" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17258,7 +17579,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C61" s="3" t="n">
@@ -17267,20 +17588,29 @@
       <c r="D61" s="4" t="n">
         <v>0.58</v>
       </c>
+      <c r="H61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="K61" s="4" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="O61" s="4" t="n">
-        <v>0.0001</v>
+        <v>0</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -17291,148 +17621,131 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E62" s="5">
-        <f>SUM(E45:E61)</f>
-        <v/>
-      </c>
-      <c r="F62" s="5">
-        <f>SUM(F45:F61)</f>
-        <v/>
-      </c>
-      <c r="G62" s="5">
-        <f>SUM(G45:G61)</f>
-        <v/>
-      </c>
-      <c r="H62" s="5">
-        <f>SUM(H45:H61)</f>
-        <v/>
-      </c>
-      <c r="I62" s="5">
-        <f>SUM(I45:I61)</f>
-        <v/>
-      </c>
-      <c r="J62" s="5">
-        <f>SUM(J45:J61)</f>
-        <v/>
-      </c>
-      <c r="K62" s="5">
-        <f>SUM(K45:K61)</f>
-        <v/>
-      </c>
-      <c r="L62" s="5">
-        <f>SUM(L45:L61)</f>
-        <v/>
-      </c>
-      <c r="M62" s="5">
-        <f>SUM(M45:M61)</f>
-        <v/>
-      </c>
-      <c r="N62" s="5">
-        <f>SUM(N45:N61)</f>
-        <v/>
-      </c>
-      <c r="O62" s="5">
-        <f>SUM(O45:O61)</f>
-        <v/>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>8750300</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>16514800</v>
+        <v>8750300</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>0.0029</v>
-      </c>
-      <c r="H63" s="4" t="n">
-        <v>0.0325</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>0.0898</v>
+        <v>0.58</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0.1142</v>
+        <v>0.0001</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>0.1433</v>
+        <v>0.0001</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>0.1433</v>
+        <v>0.0001</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.1879</v>
+        <v>0.0001</v>
       </c>
       <c r="O63" s="4" t="n">
-        <v>0.2368</v>
+        <v>0.0001</v>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v>0.0001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>16514800</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="I64" s="4" t="n">
-        <v>0.04269999999999999</v>
-      </c>
-      <c r="K64" s="4" t="n">
-        <v>0.04269999999999999</v>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v>0.04269999999999999</v>
-      </c>
-      <c r="M64" s="4" t="n">
-        <v>0.04269999999999999</v>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>0.04269999999999999</v>
-      </c>
-      <c r="O64" s="4" t="n">
-        <v>0.04269999999999999</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E64" s="5">
+        <f>SUM(E47:E63)</f>
+        <v/>
+      </c>
+      <c r="F64" s="5">
+        <f>SUM(F47:F63)</f>
+        <v/>
+      </c>
+      <c r="G64" s="5">
+        <f>SUM(G47:G63)</f>
+        <v/>
+      </c>
+      <c r="H64" s="5">
+        <f>SUM(H47:H63)</f>
+        <v/>
+      </c>
+      <c r="I64" s="5">
+        <f>SUM(I47:I63)</f>
+        <v/>
+      </c>
+      <c r="J64" s="5">
+        <f>SUM(J47:J63)</f>
+        <v/>
+      </c>
+      <c r="K64" s="5">
+        <f>SUM(K47:K63)</f>
+        <v/>
+      </c>
+      <c r="L64" s="5">
+        <f>SUM(L47:L63)</f>
+        <v/>
+      </c>
+      <c r="M64" s="5">
+        <f>SUM(M47:M63)</f>
+        <v/>
+      </c>
+      <c r="N64" s="5">
+        <f>SUM(N47:N63)</f>
+        <v/>
+      </c>
+      <c r="O64" s="5">
+        <f>SUM(O47:O63)</f>
+        <v/>
+      </c>
+      <c r="P64" s="5">
+        <f>SUM(P47:P63)</f>
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -17443,7 +17756,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
@@ -17453,34 +17766,37 @@
         <v>0.59</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.0029</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.0029</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.0029</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.0325</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.0898</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.1142</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.1433</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.1433</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.1879</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.2368</v>
+      </c>
+      <c r="P65" s="4" t="n">
+        <v>0.2888</v>
       </c>
     </row>
     <row r="66">
@@ -17491,7 +17807,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
@@ -17501,34 +17817,37 @@
         <v>0.59</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0339</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.0339</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.0339</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.0339</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.0161</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.0249</v>
+        <v>0.04269999999999999</v>
+      </c>
+      <c r="P66" s="4" t="n">
+        <v>0.04269999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -17539,7 +17858,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
@@ -17548,29 +17867,38 @@
       <c r="D67" s="4" t="n">
         <v>0.59</v>
       </c>
+      <c r="E67" s="4" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0.4926</v>
+      </c>
       <c r="G67" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.4926</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.4926</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.4926</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.4926</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.4926</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.4926</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.4926</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.4926</v>
+      </c>
+      <c r="P67" s="4" t="n">
+        <v>0.4926</v>
       </c>
     </row>
     <row r="68">
@@ -17581,7 +17909,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C68" s="3" t="n">
@@ -17590,14 +17918,38 @@
       <c r="D68" s="4" t="n">
         <v>0.59</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="K68" s="4" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>0.0161</v>
+      </c>
       <c r="M68" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0161</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0161</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>0.0022</v>
+        <v>0.0249</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>0.0293</v>
       </c>
     </row>
     <row r="69">
@@ -17608,148 +17960,131 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E69" s="5">
-        <f>SUM(E63:E68)</f>
-        <v/>
-      </c>
-      <c r="F69" s="5">
-        <f>SUM(F63:F68)</f>
-        <v/>
-      </c>
-      <c r="G69" s="5">
-        <f>SUM(G63:G68)</f>
-        <v/>
-      </c>
-      <c r="H69" s="5">
-        <f>SUM(H63:H68)</f>
-        <v/>
-      </c>
-      <c r="I69" s="5">
-        <f>SUM(I63:I68)</f>
-        <v/>
-      </c>
-      <c r="J69" s="5">
-        <f>SUM(J63:J68)</f>
-        <v/>
-      </c>
-      <c r="K69" s="5">
-        <f>SUM(K63:K68)</f>
-        <v/>
-      </c>
-      <c r="L69" s="5">
-        <f>SUM(L63:L68)</f>
-        <v/>
-      </c>
-      <c r="M69" s="5">
-        <f>SUM(M63:M68)</f>
-        <v/>
-      </c>
-      <c r="N69" s="5">
-        <f>SUM(N63:N68)</f>
-        <v/>
-      </c>
-      <c r="O69" s="5">
-        <f>SUM(O63:O68)</f>
-        <v/>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>16514800</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="K69" s="4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="M69" s="4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="O69" s="4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>3467600</v>
+        <v>16514800</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>0.0004</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="I70" s="4" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v>0.0021</v>
+        <v>0.59</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.0021</v>
+        <v>0.0022</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>0.0022</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>3467600</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="H71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="K71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="L71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="O71" s="4" t="n">
-        <v>0.0032</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E71" s="5">
+        <f>SUM(E65:E70)</f>
+        <v/>
+      </c>
+      <c r="F71" s="5">
+        <f>SUM(F65:F70)</f>
+        <v/>
+      </c>
+      <c r="G71" s="5">
+        <f>SUM(G65:G70)</f>
+        <v/>
+      </c>
+      <c r="H71" s="5">
+        <f>SUM(H65:H70)</f>
+        <v/>
+      </c>
+      <c r="I71" s="5">
+        <f>SUM(I65:I70)</f>
+        <v/>
+      </c>
+      <c r="J71" s="5">
+        <f>SUM(J65:J70)</f>
+        <v/>
+      </c>
+      <c r="K71" s="5">
+        <f>SUM(K65:K70)</f>
+        <v/>
+      </c>
+      <c r="L71" s="5">
+        <f>SUM(L65:L70)</f>
+        <v/>
+      </c>
+      <c r="M71" s="5">
+        <f>SUM(M65:M70)</f>
+        <v/>
+      </c>
+      <c r="N71" s="5">
+        <f>SUM(N65:N70)</f>
+        <v/>
+      </c>
+      <c r="O71" s="5">
+        <f>SUM(O65:O70)</f>
+        <v/>
+      </c>
+      <c r="P71" s="5">
+        <f>SUM(P65:P70)</f>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -17760,7 +18095,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C72" s="3" t="n">
@@ -17770,34 +18105,37 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0004</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>0.0204</v>
+        <v>0.0021</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>0.0021</v>
       </c>
     </row>
     <row r="73">
@@ -17808,7 +18146,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C73" s="3" t="n">
@@ -17818,39 +18156,37 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0032</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+        <v>0.0032</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>0.0032</v>
       </c>
     </row>
     <row r="74">
@@ -17861,7 +18197,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C74" s="3" t="n">
@@ -17871,34 +18207,37 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.0004</v>
+        <v>0.0204</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>0.0204</v>
       </c>
     </row>
     <row r="75">
@@ -17909,7 +18248,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C75" s="3" t="n">
@@ -17919,34 +18258,42 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>0.1798</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>0.1798</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>0.2828</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>0.2828</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0.2828</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0.2828</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>0.2828</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>0.2828</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N75" s="4" t="n">
-        <v>0.2828</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>0.2828</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P75" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -17957,7 +18304,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C76" s="3" t="n">
@@ -17966,32 +18313,38 @@
       <c r="D76" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>0.0004</v>
+      </c>
       <c r="F76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.0012</v>
+        <v>0.0004</v>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v>0.0004</v>
       </c>
     </row>
     <row r="77">
@@ -18002,7 +18355,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C77" s="3" t="n">
@@ -18011,29 +18364,38 @@
       <c r="D77" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0.1798</v>
+      </c>
       <c r="G77" s="4" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="N77" s="4" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="O77" s="4" t="n">
-        <v>0</v>
+        <v>0.2828</v>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v>0.2828</v>
       </c>
     </row>
     <row r="78">
@@ -18044,51 +18406,148 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>3467600</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>3467600</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E78" s="5">
-        <f>SUM(E70:E77)</f>
-        <v/>
-      </c>
-      <c r="F78" s="5">
-        <f>SUM(F70:F77)</f>
-        <v/>
-      </c>
-      <c r="G78" s="5">
-        <f>SUM(G70:G77)</f>
-        <v/>
-      </c>
-      <c r="H78" s="5">
-        <f>SUM(H70:H77)</f>
-        <v/>
-      </c>
-      <c r="I78" s="5">
-        <f>SUM(I70:I77)</f>
-        <v/>
-      </c>
-      <c r="J78" s="5">
-        <f>SUM(J70:J77)</f>
-        <v/>
-      </c>
-      <c r="K78" s="5">
-        <f>SUM(K70:K77)</f>
-        <v/>
-      </c>
-      <c r="L78" s="5">
-        <f>SUM(L70:L77)</f>
-        <v/>
-      </c>
-      <c r="M78" s="5">
-        <f>SUM(M70:M77)</f>
-        <v/>
-      </c>
-      <c r="N78" s="5">
-        <f>SUM(N70:N77)</f>
-        <v/>
-      </c>
-      <c r="O78" s="5">
-        <f>SUM(O70:O77)</f>
+      <c r="E80" s="5">
+        <f>SUM(E72:E79)</f>
+        <v/>
+      </c>
+      <c r="F80" s="5">
+        <f>SUM(F72:F79)</f>
+        <v/>
+      </c>
+      <c r="G80" s="5">
+        <f>SUM(G72:G79)</f>
+        <v/>
+      </c>
+      <c r="H80" s="5">
+        <f>SUM(H72:H79)</f>
+        <v/>
+      </c>
+      <c r="I80" s="5">
+        <f>SUM(I72:I79)</f>
+        <v/>
+      </c>
+      <c r="J80" s="5">
+        <f>SUM(J72:J79)</f>
+        <v/>
+      </c>
+      <c r="K80" s="5">
+        <f>SUM(K72:K79)</f>
+        <v/>
+      </c>
+      <c r="L80" s="5">
+        <f>SUM(L72:L79)</f>
+        <v/>
+      </c>
+      <c r="M80" s="5">
+        <f>SUM(M72:M79)</f>
+        <v/>
+      </c>
+      <c r="N80" s="5">
+        <f>SUM(N72:N79)</f>
+        <v/>
+      </c>
+      <c r="O80" s="5">
+        <f>SUM(O72:O79)</f>
+        <v/>
+      </c>
+      <c r="P80" s="5">
+        <f>SUM(P72:P79)</f>
         <v/>
       </c>
     </row>
@@ -18103,7 +18562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18299,13 +18758,13 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>54.47000000000001</v>
+        <v>131.73</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>76.03</v>
+        <v>191.91</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1395.814209656692</v>
+        <v>1456.843543611933</v>
       </c>
     </row>
     <row r="16">
@@ -18362,13 +18821,13 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>11410.43</v>
+        <v>12995.83</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>19863.85</v>
+        <v>22563.05</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1740.850257176986</v>
+        <v>1736.17614265499</v>
       </c>
     </row>
     <row r="19">
@@ -18425,13 +18884,13 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>370.39</v>
+        <v>371.23</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>360.8899999999999</v>
+        <v>362.6299999999999</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>974.3513593779527</v>
+        <v>976.8337688225627</v>
       </c>
     </row>
     <row r="22">
@@ -18446,13 +18905,13 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>890.5799999999999</v>
+        <v>976.3100000000002</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3859.22</v>
+        <v>4231.3</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4333.378247883403</v>
+        <v>4333.971791746473</v>
       </c>
     </row>
     <row r="23">
@@ -18488,13 +18947,13 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1631.66</v>
+        <v>1684.86</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3626.36</v>
+        <v>3744.82</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>2222.497334003408</v>
+        <v>2222.629773393635</v>
       </c>
     </row>
     <row r="25">
@@ -18509,13 +18968,13 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>9166.309999999999</v>
+        <v>9363.790000000003</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>11030</v>
+        <v>11277.32</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1203.319547342388</v>
+        <v>1204.354219819111</v>
       </c>
     </row>
     <row r="26">
@@ -18614,13 +19073,13 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>6909.340000000001</v>
+        <v>8053.429999999999</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>15023.39999999999</v>
+        <v>17702.03</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2174.361082245191</v>
+        <v>2198.073367496831</v>
       </c>
     </row>
     <row r="31">
@@ -18635,13 +19094,13 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>28.23</v>
+        <v>29.29</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>65.05000000000001</v>
+        <v>67.19000000000001</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>2304.28622033298</v>
+        <v>2293.956981905088</v>
       </c>
     </row>
     <row r="32">
@@ -18656,13 +19115,13 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>13.1</v>
+        <v>26.39</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>32.4</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>2473.282442748092</v>
+        <v>2538.461538461539</v>
       </c>
     </row>
     <row r="33">
@@ -18698,13 +19157,13 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>667.8100000000001</v>
+        <v>684.74</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>807.28</v>
+        <v>827.5700000000001</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1208.846827690511</v>
+        <v>1208.590121798055</v>
       </c>
     </row>
     <row r="35">
@@ -18803,13 +19262,13 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>8316.27</v>
+        <v>10024.86</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>15516.51</v>
+        <v>18689.38</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>1865.801615387667</v>
+        <v>1864.303341892056</v>
       </c>
     </row>
     <row r="40">
@@ -18820,17 +19279,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1880.46</v>
+        <v>6722.290000000001</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>3073.34</v>
+        <v>7449.77</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1634.355423672931</v>
+        <v>1108.219074154789</v>
       </c>
     </row>
     <row r="41">
@@ -18841,17 +19300,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1696.55</v>
+        <v>1880.46</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>2296.29</v>
+        <v>3073.34</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1353.505643806549</v>
+        <v>1634.355423672931</v>
       </c>
     </row>
     <row r="42">
@@ -18862,17 +19321,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>40.24</v>
+        <v>1730.87</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>88.01000000000001</v>
+        <v>2336.15</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>2187.127236580517</v>
+        <v>1349.696973198449</v>
       </c>
     </row>
     <row r="43">
@@ -18883,17 +19342,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>4826.12</v>
+        <v>40.24</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>9473.09</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>1962.879082990062</v>
+        <v>2187.127236580517</v>
       </c>
     </row>
     <row r="44">
@@ -18904,17 +19363,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>0.02</v>
+        <v>4841.26</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.1</v>
+        <v>9501.809999999999</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>5000</v>
+        <v>1962.672940515486</v>
       </c>
     </row>
     <row r="45">
@@ -18925,17 +19384,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>268.9</v>
+        <v>0.02</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>688.4400000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>2560.208255857196</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="46">
@@ -18946,17 +19405,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>1100.37</v>
+        <v>268.9</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>1973.56</v>
+        <v>688.4400000000001</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1793.542172178449</v>
+        <v>2560.208255857196</v>
       </c>
     </row>
     <row r="47">
@@ -18967,17 +19426,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>16122.8</v>
+        <v>1104.23</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>26867.49</v>
+        <v>1988.4</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>1666.428287890441</v>
+        <v>1800.711808228358</v>
       </c>
     </row>
     <row r="48">
@@ -18988,17 +19447,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>247.82</v>
+        <v>17414.2</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>526.8599999999999</v>
+        <v>28764.78</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>2125.978532806068</v>
+        <v>1651.80025496434</v>
       </c>
     </row>
     <row r="49">
@@ -19009,17 +19468,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>85.22</v>
+        <v>421.87</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>144.14</v>
+        <v>1032.93</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>1691.386998357193</v>
+        <v>2448.455685400716</v>
       </c>
     </row>
     <row r="50">
@@ -19030,17 +19489,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>484.85</v>
+        <v>85.22</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>926.96</v>
+        <v>144.14</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1911.849025471795</v>
+        <v>1691.386998357193</v>
       </c>
     </row>
     <row r="51">
@@ -19051,17 +19510,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>3924.77</v>
+        <v>484.85</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>4868.82</v>
+        <v>926.96</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>1240.536388119559</v>
+        <v>1911.849025471795</v>
       </c>
     </row>
     <row r="52">
@@ -19072,17 +19531,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>144.18</v>
+        <v>4515.4</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>204.36</v>
+        <v>5579.92</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1417.394923012901</v>
+        <v>1235.753200159454</v>
       </c>
     </row>
     <row r="53">
@@ -19093,17 +19552,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>0.12</v>
+        <v>455.09</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.25</v>
+        <v>644.63</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>2083.333333333333</v>
+        <v>1416.489046122745</v>
       </c>
     </row>
     <row r="54">
@@ -19114,17 +19573,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>7233.63</v>
+        <v>0.12</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>11036.6</v>
+        <v>0.25</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1525.734658808924</v>
+        <v>2083.333333333333</v>
       </c>
     </row>
     <row r="55">
@@ -19135,17 +19594,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>542.15</v>
+        <v>7295.74</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>737.62</v>
+        <v>11154.6</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>1360.545974361339</v>
+        <v>1528.91961610474</v>
       </c>
     </row>
     <row r="56">
@@ -19156,17 +19615,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>3687.78</v>
+        <v>548.09</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>4387.33</v>
+        <v>789.33</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1189.694070687514</v>
+        <v>1440.146691236841</v>
       </c>
     </row>
     <row r="57">
@@ -19177,17 +19636,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>0.33</v>
+        <v>3687.78</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>1.37</v>
+        <v>4387.33</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>4151.515151515151</v>
+        <v>1189.694070687514</v>
       </c>
     </row>
     <row r="58">
@@ -19198,17 +19657,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="D58" s="6" t="n">
         <v>1.37</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>2174.603174603174</v>
+        <v>4151.515151515151</v>
       </c>
     </row>
     <row r="59">
@@ -19219,17 +19678,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>27608.87</v>
+        <v>0.63</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>58676.85</v>
+        <v>1.37</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>2125.289807224997</v>
+        <v>2174.603174603174</v>
       </c>
     </row>
     <row r="60">
@@ -19240,38 +19699,38 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>1790.29</v>
+        <v>31487.42</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>2303.66</v>
+        <v>66814.48</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1286.752425584682</v>
+        <v>2121.94203272291</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Coated Steel Sheet</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>133.1</v>
+        <v>1891.39</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>169.14</v>
+        <v>2435.04</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>1270.773854244928</v>
+        <v>1287.434109305854</v>
       </c>
     </row>
     <row r="62">
@@ -19282,17 +19741,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>19.72</v>
+        <v>133.1</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>39.63</v>
+        <v>169.14</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>2009.634888438134</v>
+        <v>1270.773854244928</v>
       </c>
     </row>
     <row r="63">
@@ -19303,17 +19762,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>7.25</v>
+        <v>19.72</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>19.82</v>
+        <v>39.63</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>2733.793103448276</v>
+        <v>2009.634888438134</v>
       </c>
     </row>
     <row r="64">
@@ -19324,17 +19783,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>1721.39</v>
+        <v>7.31</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>1312.5</v>
+        <v>19.98</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>762.465217062955</v>
+        <v>2733.242134062928</v>
       </c>
     </row>
     <row r="65">
@@ -19345,17 +19804,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>7547.919999999998</v>
+        <v>1721.39</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>10369.13</v>
+        <v>1312.5</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1373.773171946709</v>
+        <v>762.465217062955</v>
       </c>
     </row>
     <row r="66">
@@ -19366,80 +19825,80 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>277.79</v>
+        <v>9921.959999999999</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>412.41</v>
+        <v>7484.200000000001</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1484.610677130206</v>
+        <v>754.3066087748794</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>156.55</v>
+        <v>8575.779999999999</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>339.47</v>
+        <v>11735.09</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>2168.444586394123</v>
+        <v>1368.399142701888</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>25.8</v>
+        <v>49.88</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>47.1</v>
+        <v>80.97</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1825.581395348837</v>
+        <v>1623.295910184443</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
-        <v>645.63</v>
+        <v>387.1300000000001</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>1079.21</v>
+        <v>608.04</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1671.561110852965</v>
+        <v>1570.635187146436</v>
       </c>
     </row>
     <row r="70">
@@ -19450,17 +19909,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>0.01</v>
+        <v>164.48</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>0.01</v>
+        <v>359.08</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1000</v>
+        <v>2183.122568093386</v>
       </c>
     </row>
     <row r="71">
@@ -19471,17 +19930,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>558.6899999999999</v>
+        <v>28.89</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>837.2199999999999</v>
+        <v>51.74</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1498.541230378206</v>
+        <v>1790.931118033922</v>
       </c>
     </row>
     <row r="72">
@@ -19492,17 +19951,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>62.77</v>
+        <v>645.63</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>131.18</v>
+        <v>1079.21</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>2089.851840050979</v>
+        <v>1671.561110852965</v>
       </c>
     </row>
     <row r="73">
@@ -19513,17 +19972,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>2231.47</v>
+        <v>0.01</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>2253.41</v>
+        <v>0.01</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1009.832083783336</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="74">
@@ -19534,17 +19993,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>321.41</v>
+        <v>588.84</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>335.59</v>
+        <v>881.55</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1044.118104601599</v>
+        <v>1497.095985327084</v>
       </c>
     </row>
     <row r="75">
@@ -19555,80 +20014,80 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>2228.2</v>
+        <v>63.19</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>4826.240000000002</v>
+        <v>133.25</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>2165.981509738804</v>
+        <v>2108.719734135148</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>72.08</v>
+        <v>2231.47</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>104.06</v>
+        <v>2253.41</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1443.673695893452</v>
+        <v>1009.832083783336</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>385.82</v>
+        <v>321.41</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>496.14</v>
+        <v>335.59</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>1285.936447047846</v>
+        <v>1044.118104601599</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>4164.05</v>
+        <v>2736.51</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>5554.73</v>
+        <v>5838.969999999999</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>1333.972935003182</v>
+        <v>2133.728727466736</v>
       </c>
     </row>
     <row r="79">
@@ -19639,17 +20098,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>1.83</v>
+        <v>72.08</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>5.66</v>
+        <v>104.06</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>3092.896174863388</v>
+        <v>1443.673695893452</v>
       </c>
     </row>
     <row r="80">
@@ -19660,17 +20119,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>88.08000000000001</v>
+        <v>385.82</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>147.89</v>
+        <v>496.14</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1679.041780199818</v>
+        <v>1285.936447047846</v>
       </c>
     </row>
     <row r="81">
@@ -19681,17 +20140,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
-        <v>95.56999999999999</v>
+        <v>4925.35</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>256.16</v>
+        <v>6490.3</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>2680.339018520457</v>
+        <v>1317.733765113139</v>
       </c>
     </row>
     <row r="82">
@@ -19702,17 +20161,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>193.25</v>
+        <v>1.83</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>263.71</v>
+        <v>5.66</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>1364.605433376456</v>
+        <v>3092.896174863388</v>
       </c>
     </row>
     <row r="83">
@@ -19723,17 +20182,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C83" s="6" t="n">
-        <v>93.3</v>
+        <v>88.08000000000001</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>138.03</v>
+        <v>147.89</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>1479.421221864952</v>
+        <v>1679.041780199818</v>
       </c>
     </row>
     <row r="84">
@@ -19744,122 +20203,122 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>5613.039999999997</v>
+        <v>2679.14</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>8650.640000000001</v>
+        <v>2208.72</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>1541.168422102819</v>
+        <v>824.4138044297797</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>2389.86</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>2108.23</v>
+        <v>256.16</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>882.1562769367245</v>
+        <v>2680.339018520457</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>1.15</v>
+        <v>193.25</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>2.14</v>
+        <v>263.71</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>1860.869565217391</v>
+        <v>1364.605433376456</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C87" s="6" t="n">
-        <v>168.81</v>
+        <v>93.3</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>476.47</v>
+        <v>138.03</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>2822.522362419288</v>
+        <v>1479.421221864952</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>55.54</v>
+        <v>62.38</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>81.45</v>
+        <v>89.2</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1466.510622974433</v>
+        <v>1429.945495351074</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C89" s="6" t="n">
-        <v>15.15</v>
+        <v>6593.459999999998</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>71.48</v>
+        <v>10051.92</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>4718.151815181519</v>
+        <v>1524.528851316305</v>
       </c>
     </row>
     <row r="90">
@@ -19870,17 +20329,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>824.29</v>
+        <v>2392.79</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>926.6900000000001</v>
+        <v>2113.52</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>1124.228123597278</v>
+        <v>883.2868743182646</v>
       </c>
     </row>
     <row r="91">
@@ -19891,17 +20350,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>32963.3</v>
+        <v>1.15</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>34684.28</v>
+        <v>2.14</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>1052.208971795907</v>
+        <v>1860.869565217391</v>
       </c>
     </row>
     <row r="92">
@@ -19912,17 +20371,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>7136.14</v>
+        <v>372.71</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>11455.77</v>
+        <v>1190.14</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>1605.317440521066</v>
+        <v>3193.206514448231</v>
       </c>
     </row>
     <row r="93">
@@ -19933,17 +20392,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>6789.440000000001</v>
+        <v>55.54</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>10545.34</v>
+        <v>81.45</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>1553.197318188245</v>
+        <v>1466.510622974433</v>
       </c>
     </row>
     <row r="94">
@@ -19954,17 +20413,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>2</v>
+        <v>17.44</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>3.57</v>
+        <v>82.48</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>1785</v>
+        <v>4729.357798165137</v>
       </c>
     </row>
     <row r="95">
@@ -19975,17 +20434,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C95" s="6" t="n">
-        <v>8537.370000000001</v>
+        <v>824.29</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>9890.809999999999</v>
+        <v>926.6900000000001</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>1158.531257284152</v>
+        <v>1124.228123597278</v>
       </c>
     </row>
     <row r="96">
@@ -19996,17 +20455,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>0.05</v>
+        <v>32984.2</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>0.24</v>
+        <v>34707.86</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>4800</v>
+        <v>1052.257141297955</v>
       </c>
     </row>
     <row r="97">
@@ -20017,17 +20476,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>653.25</v>
+        <v>10982.17</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>636.14</v>
+        <v>17973.24</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>973.80788365863</v>
+        <v>1636.583662427371</v>
       </c>
     </row>
     <row r="98">
@@ -20038,17 +20497,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>20116.69</v>
+        <v>7514.85</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>18313.92</v>
+        <v>11735.52</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>910.3843624373593</v>
+        <v>1561.643944988922</v>
       </c>
     </row>
     <row r="99">
@@ -20059,17 +20518,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>637.12</v>
+        <v>2</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>972.5999999999999</v>
+        <v>3.57</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>1526.557006529382</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="100">
@@ -20080,17 +20539,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>328.6</v>
+        <v>12070.4</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>437.03</v>
+        <v>14391.17</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1329.975654290932</v>
+        <v>1192.269518822905</v>
       </c>
     </row>
     <row r="101">
@@ -20101,17 +20560,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>5428.920000000002</v>
+        <v>0.05</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>14238.89</v>
+        <v>0.24</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>2622.785010646685</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="102">
@@ -20122,16 +20581,121 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>636.14</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>973.80788365863</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>20116.69</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>18313.92</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>910.3843624373593</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>637.12</v>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>972.5999999999999</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>1526.557006529382</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>437.03</v>
+      </c>
+      <c r="E105" s="6" t="n">
+        <v>1329.975654290932</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>74686.57000000001</v>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>18004.27</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>241.0643573536715</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="C102" s="6" t="n">
+      <c r="C107" s="6" t="n">
         <v>690.49</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D107" s="6" t="n">
         <v>579.4100000000001</v>
       </c>
-      <c r="E102" s="6" t="n">
+      <c r="E107" s="6" t="n">
         <v>839.1287346666861</v>
       </c>
     </row>

--- a/data/canada_trq_tracker.xlsx
+++ b/data/canada_trq_tracker.xlsx
@@ -12390,7 +12390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12476,7 +12476,12 @@
           <t>September 7 2026</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>September 14 2026</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
@@ -12532,6 +12537,9 @@
       <c r="P3" s="4" t="n">
         <v>0.3369</v>
       </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.3369</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12580,6 +12588,9 @@
       <c r="P4" s="4" t="n">
         <v>0.0396</v>
       </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.0396</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12622,6 +12633,9 @@
       <c r="P5" s="4" t="n">
         <v>0.0009</v>
       </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12682,6 +12696,10 @@
         <f>SUM(P3:P5)</f>
         <v/>
       </c>
+      <c r="Q6" s="5">
+        <f>SUM(Q3:Q5)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12733,6 +12751,9 @@
       <c r="P7" s="4" t="n">
         <v>0.3542</v>
       </c>
+      <c r="Q7" s="4" t="n">
+        <v>0.3542</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12778,6 +12799,9 @@
       <c r="P8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12802,6 +12826,9 @@
       <c r="P9" s="4" t="n">
         <v>0.3547</v>
       </c>
+      <c r="Q9" s="4" t="n">
+        <v>0.3547</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12811,158 +12838,102 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E10" s="5">
-        <f>SUM(E7:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="5">
-        <f>SUM(F7:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>SUM(G7:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="5">
-        <f>SUM(H7:H9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="5">
-        <f>SUM(I7:I9)</f>
-        <v/>
-      </c>
-      <c r="J10" s="5">
-        <f>SUM(J7:J9)</f>
-        <v/>
-      </c>
-      <c r="K10" s="5">
-        <f>SUM(K7:K9)</f>
-        <v/>
-      </c>
-      <c r="L10" s="5">
-        <f>SUM(L7:L9)</f>
-        <v/>
-      </c>
-      <c r="M10" s="5">
-        <f>SUM(M7:M9)</f>
-        <v/>
-      </c>
-      <c r="N10" s="5">
-        <f>SUM(N7:N9)</f>
-        <v/>
-      </c>
-      <c r="O10" s="5">
-        <f>SUM(O7:O9)</f>
-        <v/>
-      </c>
-      <c r="P10" s="5">
-        <f>SUM(P7:P9)</f>
-        <v/>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>5201200</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0.0002</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cold-Rolled Sheet</t>
+          <t>Steel Plate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6168400</v>
+        <v>5201200</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>0.001</v>
+        <v>0.36</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0.1897</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cold-Rolled Sheet</t>
+          <t>Steel Plate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>6168400</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0.1099</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.1099</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0.1099</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0.1135</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E12" s="5">
+        <f>SUM(E7:E11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>SUM(F7:F11)</f>
+        <v/>
+      </c>
+      <c r="G12" s="5">
+        <f>SUM(G7:G11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="5">
+        <f>SUM(H7:H11)</f>
+        <v/>
+      </c>
+      <c r="I12" s="5">
+        <f>SUM(I7:I11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="5">
+        <f>SUM(J7:J11)</f>
+        <v/>
+      </c>
+      <c r="K12" s="5">
+        <f>SUM(K7:K11)</f>
+        <v/>
+      </c>
+      <c r="L12" s="5">
+        <f>SUM(L7:L11)</f>
+        <v/>
+      </c>
+      <c r="M12" s="5">
+        <f>SUM(M7:M11)</f>
+        <v/>
+      </c>
+      <c r="N12" s="5">
+        <f>SUM(N7:N11)</f>
+        <v/>
+      </c>
+      <c r="O12" s="5">
+        <f>SUM(O7:O11)</f>
+        <v/>
+      </c>
+      <c r="P12" s="5">
+        <f>SUM(P7:P11)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="5">
+        <f>SUM(Q7:Q11)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -12973,7 +12944,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -12983,37 +12954,40 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5249</v>
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.5249</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5249</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5572</v>
+        <v>0</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5572</v>
+        <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5572</v>
+        <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5572</v>
+        <v>0</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5572</v>
+        <v>0</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.5572</v>
+        <v>0</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5222</v>
+        <v>0</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5222</v>
+        <v>0.001</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">
@@ -13024,7 +12998,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -13033,35 +13007,41 @@
       <c r="D14" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>0.1099</v>
+      </c>
       <c r="F14" s="4" t="n">
-        <v>0.0003</v>
+        <v>0.1099</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.0011</v>
+        <v>0.1099</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.1135</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.1135</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.1135</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.1135</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.1135</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.1135</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.1135</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.1135</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0.1135</v>
       </c>
     </row>
     <row r="15">
@@ -13072,7 +13052,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -13081,35 +13061,41 @@
       <c r="D15" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>0.5249</v>
+      </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
+        <v>0.5249</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>0.5249</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0</v>
+        <v>0.5572</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0</v>
+        <v>0.5572</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>0.5572</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0</v>
+        <v>0.5572</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0</v>
+        <v>0.5572</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0</v>
+        <v>0.5572</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0</v>
+        <v>0.5222</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0</v>
+        <v>0.5222</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0.5222</v>
       </c>
     </row>
     <row r="16">
@@ -13120,7 +13106,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -13130,34 +13116,37 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2191</v>
+        <v>0.0003</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2191</v>
+        <v>0.0011</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3156</v>
+        <v>0.0008</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3156</v>
+        <v>0.0008</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3156</v>
+        <v>0.0008</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3156</v>
+        <v>0.0008</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3156</v>
+        <v>0.0008</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3156</v>
+        <v>0.0008</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3156</v>
+        <v>0.0008</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3156</v>
+        <v>0.0008</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0.0008</v>
       </c>
     </row>
     <row r="17">
@@ -13168,7 +13157,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -13177,32 +13166,38 @@
       <c r="D17" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G17" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.0406</v>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13213,7 +13208,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -13222,32 +13217,38 @@
       <c r="D18" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="F18" s="4" t="n">
+        <v>0.2191</v>
+      </c>
       <c r="G18" s="4" t="n">
-        <v>0</v>
+        <v>0.2191</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0</v>
+        <v>0.3156</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0</v>
+        <v>0.3156</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>0.3156</v>
       </c>
     </row>
     <row r="19">
@@ -13258,158 +13259,156 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E19" s="5">
-        <f>SUM(E11:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="5">
-        <f>SUM(F11:F18)</f>
-        <v/>
-      </c>
-      <c r="G19" s="5">
-        <f>SUM(G11:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="5">
-        <f>SUM(H11:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="5">
-        <f>SUM(I11:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="5">
-        <f>SUM(J11:J18)</f>
-        <v/>
-      </c>
-      <c r="K19" s="5">
-        <f>SUM(K11:K18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="5">
-        <f>SUM(L11:L18)</f>
-        <v/>
-      </c>
-      <c r="M19" s="5">
-        <f>SUM(M11:M18)</f>
-        <v/>
-      </c>
-      <c r="N19" s="5">
-        <f>SUM(N11:N18)</f>
-        <v/>
-      </c>
-      <c r="O19" s="5">
-        <f>SUM(O11:O18)</f>
-        <v/>
-      </c>
-      <c r="P19" s="5">
-        <f>SUM(P11:P18)</f>
-        <v/>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>6168400</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>0.0406</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Coated Steel Sheet</t>
+          <t>Cold-Rolled Sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>18732800</v>
+        <v>6168400</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.0027</v>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Coated Steel Sheet</t>
+          <t>Cold-Rolled Sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>18732800</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>0.2673</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0.2673</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E21" s="5">
+        <f>SUM(E13:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="5">
+        <f>SUM(F13:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="5">
+        <f>SUM(G13:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="5">
+        <f>SUM(H13:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="5">
+        <f>SUM(I13:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="5">
+        <f>SUM(J13:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="5">
+        <f>SUM(K13:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="5">
+        <f>SUM(L13:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="5">
+        <f>SUM(M13:M20)</f>
+        <v/>
+      </c>
+      <c r="N21" s="5">
+        <f>SUM(N13:N20)</f>
+        <v/>
+      </c>
+      <c r="O21" s="5">
+        <f>SUM(O13:O20)</f>
+        <v/>
+      </c>
+      <c r="P21" s="5">
+        <f>SUM(P13:P20)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="5">
+        <f>SUM(Q13:Q20)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -13420,7 +13419,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
@@ -13430,37 +13429,40 @@
         <v>0.37</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0027</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>0.003</v>
       </c>
     </row>
     <row r="23">
@@ -13471,7 +13473,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
@@ -13481,37 +13483,40 @@
         <v>0.37</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.2213</v>
+        <v>0.2673</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2488</v>
+        <v>0.2673</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>0.2673</v>
       </c>
     </row>
     <row r="24">
@@ -13522,7 +13527,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -13532,37 +13537,40 @@
         <v>0.37</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.3697</v>
+        <v>0.0069</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>0.0069</v>
       </c>
     </row>
     <row r="25">
@@ -13573,7 +13581,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -13583,37 +13591,40 @@
         <v>0.37</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2213</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.0289</v>
+        <v>0.2488</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>0.2488</v>
       </c>
     </row>
     <row r="26">
@@ -13624,7 +13635,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -13633,35 +13644,41 @@
       <c r="D26" s="4" t="n">
         <v>0.37</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>0.3697</v>
+      </c>
       <c r="F26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.3697</v>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>0.3697</v>
       </c>
     </row>
     <row r="27">
@@ -13672,163 +13689,165 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E27" s="5">
-        <f>SUM(E20:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="5">
-        <f>SUM(F20:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="5">
-        <f>SUM(G20:G26)</f>
-        <v/>
-      </c>
-      <c r="H27" s="5">
-        <f>SUM(H20:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="5">
-        <f>SUM(I20:I26)</f>
-        <v/>
-      </c>
-      <c r="J27" s="5">
-        <f>SUM(J20:J26)</f>
-        <v/>
-      </c>
-      <c r="K27" s="5">
-        <f>SUM(K20:K26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="5">
-        <f>SUM(L20:L26)</f>
-        <v/>
-      </c>
-      <c r="M27" s="5">
-        <f>SUM(M20:M26)</f>
-        <v/>
-      </c>
-      <c r="N27" s="5">
-        <f>SUM(N20:N26)</f>
-        <v/>
-      </c>
-      <c r="O27" s="5">
-        <f>SUM(O20:O26)</f>
-        <v/>
-      </c>
-      <c r="P27" s="5">
-        <f>SUM(P20:P26)</f>
-        <v/>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>18732800</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>0.0289</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Coated Steel Sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>13445100</v>
+        <v>18732800</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0.2777</v>
+        <v>0.37</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2777</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.2747</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2747</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2747</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.2747</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2747</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2747</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.29</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.29</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+        <v>0.07539999999999999</v>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Coated Steel Sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>13445100</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="M29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="P29" s="4" t="n">
-        <v>0.0037</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E29" s="5">
+        <f>SUM(E22:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="5">
+        <f>SUM(F22:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="5">
+        <f>SUM(G22:G28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="5">
+        <f>SUM(H22:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="5">
+        <f>SUM(I22:I28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="5">
+        <f>SUM(J22:J28)</f>
+        <v/>
+      </c>
+      <c r="K29" s="5">
+        <f>SUM(K22:K28)</f>
+        <v/>
+      </c>
+      <c r="L29" s="5">
+        <f>SUM(L22:L28)</f>
+        <v/>
+      </c>
+      <c r="M29" s="5">
+        <f>SUM(M22:M28)</f>
+        <v/>
+      </c>
+      <c r="N29" s="5">
+        <f>SUM(N22:N28)</f>
+        <v/>
+      </c>
+      <c r="O29" s="5">
+        <f>SUM(O22:O28)</f>
+        <v/>
+      </c>
+      <c r="P29" s="5">
+        <f>SUM(P22:P28)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="5">
+        <f>SUM(Q22:Q28)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -13839,7 +13858,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
@@ -13849,37 +13868,45 @@
         <v>0.29</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.2777</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.2777</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.2747</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.2747</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.2747</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.2747</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.2747</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.2747</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.29</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.29</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.29</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -13890,7 +13917,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
@@ -13900,37 +13927,40 @@
         <v>0.29</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.0883</v>
+        <v>0.0037</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>0.0037</v>
       </c>
     </row>
     <row r="32">
@@ -13941,7 +13971,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -13950,29 +13980,41 @@
       <c r="D32" s="4" t="n">
         <v>0.29</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.2899</v>
+      </c>
       <c r="H32" s="4" t="n">
-        <v>0.0038</v>
+        <v>0.2899</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.0038</v>
+        <v>0.2899</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.0038</v>
+        <v>0.2899</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.0038</v>
+        <v>0.2899</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.0038</v>
+        <v>0.2899</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.0038</v>
+        <v>0.2899</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.0038</v>
+        <v>0.2899</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.0075</v>
+        <v>0.2899</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>0.2899</v>
       </c>
     </row>
     <row r="33">
@@ -13983,7 +14025,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
@@ -13992,8 +14034,41 @@
       <c r="D33" s="4" t="n">
         <v>0.29</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
       <c r="P33" s="4" t="n">
-        <v>0.2822</v>
+        <v>0.0883</v>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>0.0883</v>
       </c>
     </row>
     <row r="34">
@@ -14004,163 +14079,129 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E34" s="5">
-        <f>SUM(E28:E33)</f>
-        <v/>
-      </c>
-      <c r="F34" s="5">
-        <f>SUM(F28:F33)</f>
-        <v/>
-      </c>
-      <c r="G34" s="5">
-        <f>SUM(G28:G33)</f>
-        <v/>
-      </c>
-      <c r="H34" s="5">
-        <f>SUM(H28:H33)</f>
-        <v/>
-      </c>
-      <c r="I34" s="5">
-        <f>SUM(I28:I33)</f>
-        <v/>
-      </c>
-      <c r="J34" s="5">
-        <f>SUM(J28:J33)</f>
-        <v/>
-      </c>
-      <c r="K34" s="5">
-        <f>SUM(K28:K33)</f>
-        <v/>
-      </c>
-      <c r="L34" s="5">
-        <f>SUM(L28:L33)</f>
-        <v/>
-      </c>
-      <c r="M34" s="5">
-        <f>SUM(M28:M33)</f>
-        <v/>
-      </c>
-      <c r="N34" s="5">
-        <f>SUM(N28:N33)</f>
-        <v/>
-      </c>
-      <c r="O34" s="5">
-        <f>SUM(O28:O33)</f>
-        <v/>
-      </c>
-      <c r="P34" s="5">
-        <f>SUM(P28:P33)</f>
-        <v/>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>13445100</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>0.0113</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>5886100</v>
+        <v>13445100</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>0.1023</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>0.1475</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>0.1559</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="N35" s="4" t="n">
-        <v>0.1576</v>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>0.1576</v>
+        <v>0.29</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1576</v>
+        <v>0.2822</v>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>0.2822</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>5886100</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0.1828</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>0.1862</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E36" s="5">
+        <f>SUM(E30:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="5">
+        <f>SUM(F30:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="5">
+        <f>SUM(G30:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="5">
+        <f>SUM(H30:H35)</f>
+        <v/>
+      </c>
+      <c r="I36" s="5">
+        <f>SUM(I30:I35)</f>
+        <v/>
+      </c>
+      <c r="J36" s="5">
+        <f>SUM(J30:J35)</f>
+        <v/>
+      </c>
+      <c r="K36" s="5">
+        <f>SUM(K30:K35)</f>
+        <v/>
+      </c>
+      <c r="L36" s="5">
+        <f>SUM(L30:L35)</f>
+        <v/>
+      </c>
+      <c r="M36" s="5">
+        <f>SUM(M30:M35)</f>
+        <v/>
+      </c>
+      <c r="N36" s="5">
+        <f>SUM(N30:N35)</f>
+        <v/>
+      </c>
+      <c r="O36" s="5">
+        <f>SUM(O30:O35)</f>
+        <v/>
+      </c>
+      <c r="P36" s="5">
+        <f>SUM(P30:P35)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="5">
+        <f>SUM(Q30:Q35)</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -14171,7 +14212,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
@@ -14181,42 +14222,40 @@
         <v>0.42</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1023</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.147</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1475</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1559</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1576</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+        <v>0.1576</v>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>0.1576</v>
       </c>
     </row>
     <row r="38">
@@ -14227,7 +14266,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
@@ -14236,35 +14275,46 @@
       <c r="D38" s="4" t="n">
         <v>0.42</v>
       </c>
+      <c r="E38" s="4" t="n">
+        <v>0.1828</v>
+      </c>
       <c r="F38" s="4" t="n">
-        <v>0.0009</v>
+        <v>0.1862</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0.0032</v>
+        <v>0.42</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.0024</v>
+        <v>0.42</v>
+      </c>
+      <c r="Q38" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -14275,136 +14325,170 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E39" s="5">
-        <f>SUM(E35:E38)</f>
-        <v/>
-      </c>
-      <c r="F39" s="5">
-        <f>SUM(F35:F38)</f>
-        <v/>
-      </c>
-      <c r="G39" s="5">
-        <f>SUM(G35:G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="5">
-        <f>SUM(H35:H38)</f>
-        <v/>
-      </c>
-      <c r="I39" s="5">
-        <f>SUM(I35:I38)</f>
-        <v/>
-      </c>
-      <c r="J39" s="5">
-        <f>SUM(J35:J38)</f>
-        <v/>
-      </c>
-      <c r="K39" s="5">
-        <f>SUM(K35:K38)</f>
-        <v/>
-      </c>
-      <c r="L39" s="5">
-        <f>SUM(L35:L38)</f>
-        <v/>
-      </c>
-      <c r="M39" s="5">
-        <f>SUM(M35:M38)</f>
-        <v/>
-      </c>
-      <c r="N39" s="5">
-        <f>SUM(N35:N38)</f>
-        <v/>
-      </c>
-      <c r="O39" s="5">
-        <f>SUM(O35:O38)</f>
-        <v/>
-      </c>
-      <c r="P39" s="5">
-        <f>SUM(P35:P38)</f>
-        <v/>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>5886100</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1571700</v>
+        <v>5886100</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0.0024</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>0.0397</v>
+        <v>0.0024</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.2893</v>
+        <v>0.0024</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.2893</v>
+        <v>0.0024</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.2893</v>
+        <v>0.0024</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.3746</v>
+        <v>0.0024</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.3746</v>
+        <v>0.0024</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.3746</v>
+        <v>0.0024</v>
+      </c>
+      <c r="Q40" s="4" t="n">
+        <v>0.0024</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>1571700</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K41" s="4" t="n">
-        <v>0.0924</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>0.1692</v>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>0.1692</v>
-      </c>
-      <c r="N41" s="4" t="n">
-        <v>0.2455</v>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>0.2455</v>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E41" s="5">
+        <f>SUM(E37:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="5">
+        <f>SUM(F37:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="5">
+        <f>SUM(G37:G40)</f>
+        <v/>
+      </c>
+      <c r="H41" s="5">
+        <f>SUM(H37:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="5">
+        <f>SUM(I37:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="5">
+        <f>SUM(J37:J40)</f>
+        <v/>
+      </c>
+      <c r="K41" s="5">
+        <f>SUM(K37:K40)</f>
+        <v/>
+      </c>
+      <c r="L41" s="5">
+        <f>SUM(L37:L40)</f>
+        <v/>
+      </c>
+      <c r="M41" s="5">
+        <f>SUM(M37:M40)</f>
+        <v/>
+      </c>
+      <c r="N41" s="5">
+        <f>SUM(N37:N40)</f>
+        <v/>
+      </c>
+      <c r="O41" s="5">
+        <f>SUM(O37:O40)</f>
+        <v/>
+      </c>
+      <c r="P41" s="5">
+        <f>SUM(P37:P40)</f>
+        <v/>
+      </c>
+      <c r="Q41" s="5">
+        <f>SUM(Q37:Q40)</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -14415,158 +14499,146 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E42" s="5">
-        <f>SUM(E40:E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="5">
-        <f>SUM(F40:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="5">
-        <f>SUM(G40:G41)</f>
-        <v/>
-      </c>
-      <c r="H42" s="5">
-        <f>SUM(H40:H41)</f>
-        <v/>
-      </c>
-      <c r="I42" s="5">
-        <f>SUM(I40:I41)</f>
-        <v/>
-      </c>
-      <c r="J42" s="5">
-        <f>SUM(J40:J41)</f>
-        <v/>
-      </c>
-      <c r="K42" s="5">
-        <f>SUM(K40:K41)</f>
-        <v/>
-      </c>
-      <c r="L42" s="5">
-        <f>SUM(L40:L41)</f>
-        <v/>
-      </c>
-      <c r="M42" s="5">
-        <f>SUM(M40:M41)</f>
-        <v/>
-      </c>
-      <c r="N42" s="5">
-        <f>SUM(N40:N41)</f>
-        <v/>
-      </c>
-      <c r="O42" s="5">
-        <f>SUM(O40:O41)</f>
-        <v/>
-      </c>
-      <c r="P42" s="5">
-        <f>SUM(P40:P41)</f>
-        <v/>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1571700</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0.0397</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>0.4069</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>3753500</v>
+        <v>1571700</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>0.0218</v>
+        <v>0.45</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.0924</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.1692</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.1692</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.2455</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.2455</v>
       </c>
       <c r="P43" s="4" t="n">
-        <v>0.0146</v>
+        <v>0.45</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>3753500</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0.1828</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>0.1828</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>0.1828</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>0.1983</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>0.1993</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>0.1993</v>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>0.1993</v>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>0.2009</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>0.2009</v>
-      </c>
-      <c r="O44" s="4" t="n">
-        <v>0.2009</v>
-      </c>
-      <c r="P44" s="4" t="n">
-        <v>0.2065</v>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E44" s="5">
+        <f>SUM(E42:E43)</f>
+        <v/>
+      </c>
+      <c r="F44" s="5">
+        <f>SUM(F42:F43)</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>SUM(G42:G43)</f>
+        <v/>
+      </c>
+      <c r="H44" s="5">
+        <f>SUM(H42:H43)</f>
+        <v/>
+      </c>
+      <c r="I44" s="5">
+        <f>SUM(I42:I43)</f>
+        <v/>
+      </c>
+      <c r="J44" s="5">
+        <f>SUM(J42:J43)</f>
+        <v/>
+      </c>
+      <c r="K44" s="5">
+        <f>SUM(K42:K43)</f>
+        <v/>
+      </c>
+      <c r="L44" s="5">
+        <f>SUM(L42:L43)</f>
+        <v/>
+      </c>
+      <c r="M44" s="5">
+        <f>SUM(M42:M43)</f>
+        <v/>
+      </c>
+      <c r="N44" s="5">
+        <f>SUM(N42:N43)</f>
+        <v/>
+      </c>
+      <c r="O44" s="5">
+        <f>SUM(O42:O43)</f>
+        <v/>
+      </c>
+      <c r="P44" s="5">
+        <f>SUM(P42:P43)</f>
+        <v/>
+      </c>
+      <c r="Q44" s="5">
+        <f>SUM(Q42:Q43)</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -14577,7 +14649,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C45" s="3" t="n">
@@ -14587,37 +14659,40 @@
         <v>0.52</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0218</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0218</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0218</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0218</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0218</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0146</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0146</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0146</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0146</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0146</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>0.3483</v>
+        <v>0.0146</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>0.0146</v>
       </c>
     </row>
     <row r="46">
@@ -14628,7 +14703,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C46" s="3" t="n">
@@ -14638,37 +14713,40 @@
         <v>0.52</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.1828</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.1828</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.1828</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.1983</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.1993</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.1993</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.1993</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.2009</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.2009</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.2009</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>0.4306</v>
+        <v>0.2065</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0.2065</v>
       </c>
     </row>
     <row r="47">
@@ -14679,55 +14757,167 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>3753500</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3753500</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="K48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E47" s="5">
-        <f>SUM(E43:E46)</f>
-        <v/>
-      </c>
-      <c r="F47" s="5">
-        <f>SUM(F43:F46)</f>
-        <v/>
-      </c>
-      <c r="G47" s="5">
-        <f>SUM(G43:G46)</f>
-        <v/>
-      </c>
-      <c r="H47" s="5">
-        <f>SUM(H43:H46)</f>
-        <v/>
-      </c>
-      <c r="I47" s="5">
-        <f>SUM(I43:I46)</f>
-        <v/>
-      </c>
-      <c r="J47" s="5">
-        <f>SUM(J43:J46)</f>
-        <v/>
-      </c>
-      <c r="K47" s="5">
-        <f>SUM(K43:K46)</f>
-        <v/>
-      </c>
-      <c r="L47" s="5">
-        <f>SUM(L43:L46)</f>
-        <v/>
-      </c>
-      <c r="M47" s="5">
-        <f>SUM(M43:M46)</f>
-        <v/>
-      </c>
-      <c r="N47" s="5">
-        <f>SUM(N43:N46)</f>
-        <v/>
-      </c>
-      <c r="O47" s="5">
-        <f>SUM(O43:O46)</f>
-        <v/>
-      </c>
-      <c r="P47" s="5">
-        <f>SUM(P43:P46)</f>
+      <c r="E49" s="5">
+        <f>SUM(E45:E48)</f>
+        <v/>
+      </c>
+      <c r="F49" s="5">
+        <f>SUM(F45:F48)</f>
+        <v/>
+      </c>
+      <c r="G49" s="5">
+        <f>SUM(G45:G48)</f>
+        <v/>
+      </c>
+      <c r="H49" s="5">
+        <f>SUM(H45:H48)</f>
+        <v/>
+      </c>
+      <c r="I49" s="5">
+        <f>SUM(I45:I48)</f>
+        <v/>
+      </c>
+      <c r="J49" s="5">
+        <f>SUM(J45:J48)</f>
+        <v/>
+      </c>
+      <c r="K49" s="5">
+        <f>SUM(K45:K48)</f>
+        <v/>
+      </c>
+      <c r="L49" s="5">
+        <f>SUM(L45:L48)</f>
+        <v/>
+      </c>
+      <c r="M49" s="5">
+        <f>SUM(M45:M48)</f>
+        <v/>
+      </c>
+      <c r="N49" s="5">
+        <f>SUM(N45:N48)</f>
+        <v/>
+      </c>
+      <c r="O49" s="5">
+        <f>SUM(O45:O48)</f>
+        <v/>
+      </c>
+      <c r="P49" s="5">
+        <f>SUM(P45:P48)</f>
+        <v/>
+      </c>
+      <c r="Q49" s="5">
+        <f>SUM(Q45:Q48)</f>
         <v/>
       </c>
     </row>
@@ -14742,7 +14932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14828,7 +15018,12 @@
           <t>September 7 2026</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>September 14 2026</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
@@ -14884,6 +15079,9 @@
       <c r="P3" s="4" t="n">
         <v>0.3165</v>
       </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.3165</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14935,6 +15133,9 @@
       <c r="P4" s="4" t="n">
         <v>0.6835</v>
       </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.6835</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14995,6 +15196,10 @@
         <f>SUM(P3:P4)</f>
         <v/>
       </c>
+      <c r="Q5" s="5">
+        <f>SUM(Q3:Q4)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15046,6 +15251,9 @@
       <c r="P6" s="4" t="n">
         <v>0.0452</v>
       </c>
+      <c r="Q6" s="4" t="n">
+        <v>0.0452</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15097,6 +15305,9 @@
       <c r="P7" s="4" t="n">
         <v>0.0261</v>
       </c>
+      <c r="Q7" s="4" t="n">
+        <v>0.0261</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15148,6 +15359,9 @@
       <c r="P8" s="4" t="n">
         <v>0.0009</v>
       </c>
+      <c r="Q8" s="4" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15199,6 +15413,9 @@
       <c r="P9" s="4" t="n">
         <v>0.0142</v>
       </c>
+      <c r="Q9" s="4" t="n">
+        <v>0.0142</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15250,6 +15467,9 @@
       <c r="P10" s="4" t="n">
         <v>0.2225</v>
       </c>
+      <c r="Q10" s="4" t="n">
+        <v>0.2225</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15301,6 +15521,9 @@
       <c r="P11" s="4" t="n">
         <v>0.2087</v>
       </c>
+      <c r="Q11" s="4" t="n">
+        <v>0.2101</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15352,6 +15575,9 @@
       <c r="P12" s="4" t="n">
         <v>0.08310000000000001</v>
       </c>
+      <c r="Q12" s="4" t="n">
+        <v>0.08310000000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15403,7 +15629,10 @@
       <c r="P13" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -15459,6 +15688,9 @@
       <c r="P14" s="4" t="n">
         <v>0.001</v>
       </c>
+      <c r="Q14" s="4" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15510,6 +15742,9 @@
       <c r="P15" s="4" t="n">
         <v>0.0624</v>
       </c>
+      <c r="Q15" s="4" t="n">
+        <v>0.0624</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15558,6 +15793,9 @@
       <c r="P16" s="4" t="n">
         <v>0.0013</v>
       </c>
+      <c r="Q16" s="4" t="n">
+        <v>0.0013</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15618,6 +15856,10 @@
         <f>SUM(P6:P16)</f>
         <v/>
       </c>
+      <c r="Q17" s="5">
+        <f>SUM(Q6:Q16)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15669,6 +15911,9 @@
       <c r="P18" s="4" t="n">
         <v>0.0276</v>
       </c>
+      <c r="Q18" s="4" t="n">
+        <v>0.0276</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15720,6 +15965,9 @@
       <c r="P19" s="4" t="n">
         <v>0.2098</v>
       </c>
+      <c r="Q19" s="4" t="n">
+        <v>0.2141</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15771,6 +16019,9 @@
       <c r="P20" s="4" t="n">
         <v>0.0175</v>
       </c>
+      <c r="Q20" s="4" t="n">
+        <v>0.0175</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15819,6 +16070,14 @@
       <c r="P21" s="4" t="n">
         <v>0.3302</v>
       </c>
+      <c r="Q21" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15852,6 +16111,9 @@
       <c r="P22" s="4" t="n">
         <v>0.0043</v>
       </c>
+      <c r="Q22" s="4" t="n">
+        <v>0.0043</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15879,6 +16141,9 @@
       <c r="P23" s="4" t="n">
         <v>0.0086</v>
       </c>
+      <c r="Q23" s="4" t="n">
+        <v>0.0086</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15900,6 +16165,9 @@
       <c r="P24" s="4" t="n">
         <v>0.006</v>
       </c>
+      <c r="Q24" s="4" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15960,6 +16228,10 @@
         <f>SUM(P18:P24)</f>
         <v/>
       </c>
+      <c r="Q25" s="5">
+        <f>SUM(Q18:Q24)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16011,6 +16283,9 @@
       <c r="P26" s="4" t="n">
         <v>0.2462</v>
       </c>
+      <c r="Q26" s="4" t="n">
+        <v>0.2462</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16062,6 +16337,9 @@
       <c r="P27" s="4" t="n">
         <v>0.0911</v>
       </c>
+      <c r="Q27" s="4" t="n">
+        <v>0.08960000000000001</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16113,7 +16391,10 @@
       <c r="P28" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -16169,6 +16450,9 @@
       <c r="P29" s="4" t="n">
         <v>0.04940000000000001</v>
       </c>
+      <c r="Q29" s="4" t="n">
+        <v>0.04940000000000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16220,6 +16504,9 @@
       <c r="P30" s="4" t="n">
         <v>0.0533</v>
       </c>
+      <c r="Q30" s="4" t="n">
+        <v>0.0533</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16271,6 +16558,9 @@
       <c r="P31" s="4" t="n">
         <v>0.0294</v>
       </c>
+      <c r="Q31" s="4" t="n">
+        <v>0.1124</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16319,6 +16609,9 @@
       <c r="P32" s="4" t="n">
         <v>0.1044</v>
       </c>
+      <c r="Q32" s="4" t="n">
+        <v>0.1044</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16367,6 +16660,9 @@
       <c r="P33" s="4" t="n">
         <v>0.0226</v>
       </c>
+      <c r="Q33" s="4" t="n">
+        <v>0.0226</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16415,6 +16711,9 @@
       <c r="P34" s="4" t="n">
         <v>0.0369</v>
       </c>
+      <c r="Q34" s="4" t="n">
+        <v>0.0369</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16460,6 +16759,9 @@
       <c r="P35" s="4" t="n">
         <v>0.0014</v>
       </c>
+      <c r="Q35" s="4" t="n">
+        <v>0.0014</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16496,6 +16798,9 @@
       <c r="P36" s="4" t="n">
         <v>0.0063</v>
       </c>
+      <c r="Q36" s="4" t="n">
+        <v>0.0273</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16523,6 +16828,9 @@
       <c r="P37" s="4" t="n">
         <v>0.0027</v>
       </c>
+      <c r="Q37" s="4" t="n">
+        <v>0.0027</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16550,6 +16858,9 @@
       <c r="P38" s="4" t="n">
         <v>0.0002</v>
       </c>
+      <c r="Q38" s="4" t="n">
+        <v>0.0002</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16574,6 +16885,9 @@
       <c r="P39" s="4" t="n">
         <v>0.0005999999999999999</v>
       </c>
+      <c r="Q39" s="4" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16634,6 +16948,10 @@
         <f>SUM(P26:P39)</f>
         <v/>
       </c>
+      <c r="Q40" s="5">
+        <f>SUM(Q26:Q39)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16685,6 +17003,9 @@
       <c r="P41" s="4" t="n">
         <v>0.2142</v>
       </c>
+      <c r="Q41" s="4" t="n">
+        <v>0.2142</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16736,6 +17057,9 @@
       <c r="P42" s="4" t="n">
         <v>0.3459</v>
       </c>
+      <c r="Q42" s="4" t="n">
+        <v>0.3459</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16784,6 +17108,9 @@
       <c r="P43" s="4" t="n">
         <v>0.0007000000000000001</v>
       </c>
+      <c r="Q43" s="4" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16820,6 +17147,9 @@
       <c r="P44" s="4" t="n">
         <v>0.4389</v>
       </c>
+      <c r="Q44" s="4" t="n">
+        <v>0.4389</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16841,6 +17171,9 @@
       <c r="P45" s="4" t="n">
         <v>0.0003</v>
       </c>
+      <c r="Q45" s="4" t="n">
+        <v>0.0003</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16901,6 +17234,10 @@
         <f>SUM(P41:P45)</f>
         <v/>
       </c>
+      <c r="Q46" s="5">
+        <f>SUM(Q41:Q45)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16952,6 +17289,9 @@
       <c r="P47" s="4" t="n">
         <v>0.0025</v>
       </c>
+      <c r="Q47" s="4" t="n">
+        <v>0.0025</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -17003,6 +17343,9 @@
       <c r="P48" s="4" t="n">
         <v>0.4215</v>
       </c>
+      <c r="Q48" s="4" t="n">
+        <v>0.4215</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17054,6 +17397,9 @@
       <c r="P49" s="4" t="n">
         <v>0.1712</v>
       </c>
+      <c r="Q49" s="4" t="n">
+        <v>0.1712</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17105,6 +17451,9 @@
       <c r="P50" s="4" t="n">
         <v>0.016</v>
       </c>
+      <c r="Q50" s="4" t="n">
+        <v>0.016</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17156,6 +17505,9 @@
       <c r="P51" s="4" t="n">
         <v>0.0133</v>
       </c>
+      <c r="Q51" s="4" t="n">
+        <v>0.0133</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17207,6 +17559,9 @@
       <c r="P52" s="4" t="n">
         <v>0.0708</v>
       </c>
+      <c r="Q52" s="4" t="n">
+        <v>0.0708</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17255,6 +17610,9 @@
       <c r="P53" s="4" t="n">
         <v>0.0072</v>
       </c>
+      <c r="Q53" s="4" t="n">
+        <v>0.0072</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17303,6 +17661,9 @@
       <c r="P54" s="4" t="n">
         <v>0.2923</v>
       </c>
+      <c r="Q54" s="4" t="n">
+        <v>0.2923</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17348,6 +17709,9 @@
       <c r="P55" s="4" t="n">
         <v>0.0001</v>
       </c>
+      <c r="Q55" s="4" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17393,6 +17757,9 @@
       <c r="P56" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q56" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17438,6 +17805,9 @@
       <c r="P57" s="4" t="n">
         <v>0.0022</v>
       </c>
+      <c r="Q57" s="4" t="n">
+        <v>0.0022</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17483,6 +17853,9 @@
       <c r="P58" s="4" t="n">
         <v>0.0004</v>
       </c>
+      <c r="Q58" s="4" t="n">
+        <v>0.0004</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17528,6 +17901,9 @@
       <c r="P59" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q59" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17570,6 +17946,9 @@
       <c r="P60" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q60" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17612,6 +17991,9 @@
       <c r="P61" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q61" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17651,6 +18033,9 @@
       <c r="P62" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q62" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17687,6 +18072,9 @@
       <c r="P63" s="4" t="n">
         <v>0.0001</v>
       </c>
+      <c r="Q63" s="4" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17747,6 +18135,10 @@
         <f>SUM(P47:P63)</f>
         <v/>
       </c>
+      <c r="Q64" s="5">
+        <f>SUM(Q47:Q63)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17798,6 +18190,9 @@
       <c r="P65" s="4" t="n">
         <v>0.2888</v>
       </c>
+      <c r="Q65" s="4" t="n">
+        <v>0.3348</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17849,6 +18244,9 @@
       <c r="P66" s="4" t="n">
         <v>0.04269999999999999</v>
       </c>
+      <c r="Q66" s="4" t="n">
+        <v>0.0698</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17900,6 +18298,9 @@
       <c r="P67" s="4" t="n">
         <v>0.4926</v>
       </c>
+      <c r="Q67" s="4" t="n">
+        <v>0.4926</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17951,6 +18352,9 @@
       <c r="P68" s="4" t="n">
         <v>0.0293</v>
       </c>
+      <c r="Q68" s="4" t="n">
+        <v>0.0293</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17996,6 +18400,9 @@
       <c r="P69" s="4" t="n">
         <v>0.008500000000000001</v>
       </c>
+      <c r="Q69" s="4" t="n">
+        <v>0.008500000000000001</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18026,6 +18433,9 @@
       <c r="P70" s="4" t="n">
         <v>0.0022</v>
       </c>
+      <c r="Q70" s="4" t="n">
+        <v>0.0022</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18086,6 +18496,10 @@
         <f>SUM(P65:P70)</f>
         <v/>
       </c>
+      <c r="Q71" s="5">
+        <f>SUM(Q65:Q70)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18137,6 +18551,9 @@
       <c r="P72" s="4" t="n">
         <v>0.0021</v>
       </c>
+      <c r="Q72" s="4" t="n">
+        <v>0.0021</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18188,6 +18605,9 @@
       <c r="P73" s="4" t="n">
         <v>0.0032</v>
       </c>
+      <c r="Q73" s="4" t="n">
+        <v>0.0032</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18239,6 +18659,9 @@
       <c r="P74" s="4" t="n">
         <v>0.0204</v>
       </c>
+      <c r="Q74" s="4" t="n">
+        <v>0.0204</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18290,7 +18713,10 @@
       <c r="P75" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q75" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="R75" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -18346,6 +18772,9 @@
       <c r="P76" s="4" t="n">
         <v>0.0004</v>
       </c>
+      <c r="Q76" s="4" t="n">
+        <v>0.0004</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18397,6 +18826,9 @@
       <c r="P77" s="4" t="n">
         <v>0.2828</v>
       </c>
+      <c r="Q77" s="4" t="n">
+        <v>0.2828</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18445,6 +18877,9 @@
       <c r="P78" s="4" t="n">
         <v>0.0012</v>
       </c>
+      <c r="Q78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18490,6 +18925,9 @@
       <c r="P79" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="Q79" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18548,6 +18986,10 @@
       </c>
       <c r="P80" s="5">
         <f>SUM(P72:P79)</f>
+        <v/>
+      </c>
+      <c r="Q80" s="5">
+        <f>SUM(Q72:Q79)</f>
         <v/>
       </c>
     </row>
@@ -18562,7 +19004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18821,13 +19263,13 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>12995.83</v>
+        <v>14409.51</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>22563.05</v>
+        <v>25027</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1736.17614265499</v>
+        <v>1736.839073639562</v>
       </c>
     </row>
     <row r="19">
@@ -18884,13 +19326,13 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>371.23</v>
+        <v>371.37</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>362.6299999999999</v>
+        <v>362.8699999999999</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>976.8337688225627</v>
+        <v>977.1117753184154</v>
       </c>
     </row>
     <row r="22">
@@ -18905,13 +19347,13 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>976.3100000000002</v>
+        <v>971.6500000000001</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4231.3</v>
+        <v>4207.960000000001</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4333.971791746473</v>
+        <v>4330.736376267175</v>
       </c>
     </row>
     <row r="23">
@@ -19010,13 +19452,13 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>60.39</v>
+        <v>70.61999999999999</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>144.01</v>
+        <v>176.62</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>2384.666335486007</v>
+        <v>2500.991220617389</v>
       </c>
     </row>
     <row r="28">
@@ -19073,13 +19515,13 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>8053.429999999999</v>
+        <v>9083.459999999999</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>17702.03</v>
+        <v>20469.96</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2198.073367496831</v>
+        <v>2253.542152439709</v>
       </c>
     </row>
     <row r="31">
@@ -19094,13 +19536,13 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>29.29</v>
+        <v>36.85999999999999</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>67.19000000000001</v>
+        <v>84.98</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>2293.956981905088</v>
+        <v>2305.480195333696</v>
       </c>
     </row>
     <row r="32">
@@ -19136,13 +19578,13 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>2042.58</v>
+        <v>2207.17</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>3118.93</v>
+        <v>3376.13</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1526.956104534461</v>
+        <v>1529.619376849087</v>
       </c>
     </row>
     <row r="34">
@@ -19262,13 +19704,13 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>10024.86</v>
+        <v>11411.46</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>18689.38</v>
+        <v>21267.10999999999</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>1864.303341892056</v>
+        <v>1863.662493668645</v>
       </c>
     </row>
     <row r="40">
@@ -19325,13 +19767,13 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1730.87</v>
+        <v>1795.37</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>2336.15</v>
+        <v>2421.72</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>1349.696973198449</v>
+        <v>1348.869592340298</v>
       </c>
     </row>
     <row r="43">
@@ -19346,13 +19788,13 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>40.24</v>
+        <v>77.38</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>88.01000000000001</v>
+        <v>165.94</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>2187.127236580517</v>
+        <v>2144.481778237271</v>
       </c>
     </row>
     <row r="44">
@@ -19409,13 +19851,13 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>268.9</v>
+        <v>285.25</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>688.4400000000001</v>
+        <v>762.29</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>2560.208255857196</v>
+        <v>2672.357581069237</v>
       </c>
     </row>
     <row r="47">
@@ -19451,13 +19893,13 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>17414.2</v>
+        <v>17416.15</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>28764.78</v>
+        <v>28775.74</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1651.80025496434</v>
+        <v>1652.244612041122</v>
       </c>
     </row>
     <row r="49">
@@ -19472,13 +19914,13 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>421.87</v>
+        <v>663.12</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1032.93</v>
+        <v>1537.45</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>2448.455685400716</v>
+        <v>2318.509470382435</v>
       </c>
     </row>
     <row r="50">
@@ -19514,13 +19956,13 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>484.85</v>
+        <v>488.37</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>926.96</v>
+        <v>940.9100000000001</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>1911.849025471795</v>
+        <v>1926.633495095931</v>
       </c>
     </row>
     <row r="52">
@@ -19535,13 +19977,13 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>4515.4</v>
+        <v>4562.59</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>5579.92</v>
+        <v>5650.14</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1235.753200159454</v>
+        <v>1238.362421344017</v>
       </c>
     </row>
     <row r="53">
@@ -19552,17 +19994,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>455.09</v>
+        <v>5.02</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>644.63</v>
+        <v>24.36</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>1416.489046122745</v>
+        <v>4852.589641434263</v>
       </c>
     </row>
     <row r="54">
@@ -19573,17 +20015,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>0.12</v>
+        <v>455.09</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.25</v>
+        <v>644.63</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>2083.333333333333</v>
+        <v>1416.489046122745</v>
       </c>
     </row>
     <row r="55">
@@ -19594,17 +20036,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>7295.74</v>
+        <v>0.01</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>11154.6</v>
+        <v>0.03</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>1528.91961610474</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="56">
@@ -19615,17 +20057,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>548.09</v>
+        <v>0.12</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>789.33</v>
+        <v>0.25</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1440.146691236841</v>
+        <v>2083.333333333333</v>
       </c>
     </row>
     <row r="57">
@@ -19636,17 +20078,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>3687.78</v>
+        <v>7295.74</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>4387.33</v>
+        <v>11154.6</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>1189.694070687514</v>
+        <v>1528.91961610474</v>
       </c>
     </row>
     <row r="58">
@@ -19657,17 +20099,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>0.33</v>
+        <v>542.15</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1.37</v>
+        <v>737.62</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>4151.515151515151</v>
+        <v>1360.545974361339</v>
       </c>
     </row>
     <row r="59">
@@ -19678,17 +20120,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>0.63</v>
+        <v>3687.78</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1.37</v>
+        <v>4387.33</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>2174.603174603174</v>
+        <v>1189.694070687514</v>
       </c>
     </row>
     <row r="60">
@@ -19699,17 +20141,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>31487.42</v>
+        <v>0.33</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>66814.48</v>
+        <v>1.37</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>2121.94203272291</v>
+        <v>4151.515151515151</v>
       </c>
     </row>
     <row r="61">
@@ -19720,59 +20162,59 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>1891.39</v>
+        <v>15.63</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2435.04</v>
+        <v>45.93</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>1287.434109305854</v>
+        <v>2938.579654510556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Coated Steel Sheet</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>133.1</v>
+        <v>35556.35999999999</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>169.14</v>
+        <v>75316.79000000001</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1270.773854244928</v>
+        <v>2118.236793642545</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Coated Steel Sheet</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>19.72</v>
+        <v>1988.28</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>39.63</v>
+        <v>2548.99</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>2009.634888438134</v>
+        <v>1282.007564326956</v>
       </c>
     </row>
     <row r="64">
@@ -19783,17 +20225,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>7.31</v>
+        <v>133.1</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>19.98</v>
+        <v>169.14</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>2733.242134062928</v>
+        <v>1270.773854244928</v>
       </c>
     </row>
     <row r="65">
@@ -19804,17 +20246,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>1721.39</v>
+        <v>19.72</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>1312.5</v>
+        <v>39.63</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>762.465217062955</v>
+        <v>2009.634888438134</v>
       </c>
     </row>
     <row r="66">
@@ -19825,17 +20267,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>9921.959999999999</v>
+        <v>7.31</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>7484.200000000001</v>
+        <v>19.98</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>754.3066087748794</v>
+        <v>2733.242134062928</v>
       </c>
     </row>
     <row r="67">
@@ -19846,17 +20288,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>8575.779999999999</v>
+        <v>2066.03</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>11735.09</v>
+        <v>1573.68</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>1368.399142701888</v>
+        <v>761.6927150138189</v>
       </c>
     </row>
     <row r="68">
@@ -19867,17 +20309,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>49.88</v>
+        <v>9921.959999999999</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>80.97</v>
+        <v>7484.200000000001</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1623.295910184443</v>
+        <v>754.3066087748794</v>
       </c>
     </row>
     <row r="69">
@@ -19888,59 +20330,59 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
-        <v>387.1300000000001</v>
+        <v>9048.489999999998</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>608.04</v>
+        <v>12398.53</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1570.635187146436</v>
+        <v>1370.231939251743</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>164.48</v>
+        <v>49.88</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>359.08</v>
+        <v>80.97</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>2183.122568093386</v>
+        <v>1623.295910184443</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>28.89</v>
+        <v>504.5500000000001</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>51.74</v>
+        <v>739.8299999999999</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1790.931118033922</v>
+        <v>1466.316519670994</v>
       </c>
     </row>
     <row r="72">
@@ -19951,17 +20393,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>645.63</v>
+        <v>166.21</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1079.21</v>
+        <v>362.5</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>1671.561110852965</v>
+        <v>2180.975873894471</v>
       </c>
     </row>
     <row r="73">
@@ -19972,17 +20414,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>0.01</v>
+        <v>28.89</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>0.01</v>
+        <v>51.74</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1000</v>
+        <v>1790.931118033922</v>
       </c>
     </row>
     <row r="74">
@@ -19993,17 +20435,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>588.84</v>
+        <v>645.63</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>881.55</v>
+        <v>1079.21</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1497.095985327084</v>
+        <v>1671.561110852965</v>
       </c>
     </row>
     <row r="75">
@@ -20014,17 +20456,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>63.19</v>
+        <v>0.01</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>133.25</v>
+        <v>0.01</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>2108.719734135148</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="76">
@@ -20035,17 +20477,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>2231.47</v>
+        <v>680.04</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>2253.41</v>
+        <v>1020.66</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1009.832083783336</v>
+        <v>1500.882301041115</v>
       </c>
     </row>
     <row r="77">
@@ -20056,17 +20498,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>321.41</v>
+        <v>63.19</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>335.59</v>
+        <v>133.25</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>1044.118104601599</v>
+        <v>2108.719734135148</v>
       </c>
     </row>
     <row r="78">
@@ -20077,59 +20519,59 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>2736.51</v>
+        <v>2231.47</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>5838.969999999999</v>
+        <v>2253.41</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>2133.728727466736</v>
+        <v>1009.832083783336</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>72.08</v>
+        <v>321.41</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>104.06</v>
+        <v>335.59</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>1443.673695893452</v>
+        <v>1044.118104601599</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>385.82</v>
+        <v>2987</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>496.14</v>
+        <v>6399.969999999999</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1285.936447047846</v>
+        <v>2142.607967860729</v>
       </c>
     </row>
     <row r="81">
@@ -20140,17 +20582,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
-        <v>4925.35</v>
+        <v>72.08</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>6490.3</v>
+        <v>104.06</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>1317.733765113139</v>
+        <v>1443.673695893452</v>
       </c>
     </row>
     <row r="82">
@@ -20161,17 +20603,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>1.83</v>
+        <v>385.82</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>5.66</v>
+        <v>496.14</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>3092.896174863388</v>
+        <v>1285.936447047846</v>
       </c>
     </row>
     <row r="83">
@@ -20182,17 +20624,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C83" s="6" t="n">
-        <v>88.08000000000001</v>
+        <v>5714.400000000001</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>147.89</v>
+        <v>7504.52</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>1679.041780199818</v>
+        <v>1313.264734705306</v>
       </c>
     </row>
     <row r="84">
@@ -20203,17 +20645,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>2679.14</v>
+        <v>1.83</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>2208.72</v>
+        <v>5.66</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>824.4138044297797</v>
+        <v>3092.896174863388</v>
       </c>
     </row>
     <row r="85">
@@ -20224,17 +20666,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>95.56999999999999</v>
+        <v>88.08000000000001</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>256.16</v>
+        <v>147.89</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>2680.339018520457</v>
+        <v>1679.041780199818</v>
       </c>
     </row>
     <row r="86">
@@ -20245,17 +20687,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>193.25</v>
+        <v>2679.14</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>263.71</v>
+        <v>2208.72</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>1364.605433376456</v>
+        <v>824.4138044297797</v>
       </c>
     </row>
     <row r="87">
@@ -20266,17 +20708,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C87" s="6" t="n">
-        <v>93.3</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>138.03</v>
+        <v>256.16</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>1479.421221864952</v>
+        <v>2680.339018520457</v>
       </c>
     </row>
     <row r="88">
@@ -20287,17 +20729,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>62.38</v>
+        <v>193.25</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>89.2</v>
+        <v>263.71</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1429.945495351074</v>
+        <v>1364.605433376456</v>
       </c>
     </row>
     <row r="89">
@@ -20308,59 +20750,59 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C89" s="6" t="n">
-        <v>6593.459999999998</v>
+        <v>93.3</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>10051.92</v>
+        <v>138.03</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>1524.528851316305</v>
+        <v>1479.421221864952</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>2392.79</v>
+        <v>297.7</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>2113.52</v>
+        <v>389.33</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>883.2868743182646</v>
+        <v>1307.793080282163</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>1.15</v>
+        <v>7342.349999999999</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>2.14</v>
+        <v>11178.65</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>1860.869565217391</v>
+        <v>1522.489393722719</v>
       </c>
     </row>
     <row r="92">
@@ -20371,17 +20813,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>372.71</v>
+        <v>2420.79</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>1190.14</v>
+        <v>2123.93</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>3193.206514448231</v>
+        <v>877.3706104205654</v>
       </c>
     </row>
     <row r="93">
@@ -20392,17 +20834,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>55.54</v>
+        <v>1.15</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>81.45</v>
+        <v>2.14</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>1466.510622974433</v>
+        <v>1860.869565217391</v>
       </c>
     </row>
     <row r="94">
@@ -20413,17 +20855,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>17.44</v>
+        <v>388.01</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>82.48</v>
+        <v>1254.6</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>4729.357798165137</v>
+        <v>3233.421819025283</v>
       </c>
     </row>
     <row r="95">
@@ -20434,17 +20876,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C95" s="6" t="n">
-        <v>824.29</v>
+        <v>55.54</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>926.6900000000001</v>
+        <v>81.45</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>1124.228123597278</v>
+        <v>1466.510622974433</v>
       </c>
     </row>
     <row r="96">
@@ -20455,17 +20897,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>32984.2</v>
+        <v>17.16</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>34707.86</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>1052.257141297955</v>
+        <v>4719.69696969697</v>
       </c>
     </row>
     <row r="97">
@@ -20476,17 +20918,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>10982.17</v>
+        <v>824.29</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>17973.24</v>
+        <v>926.6900000000001</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>1636.583662427371</v>
+        <v>1124.228123597278</v>
       </c>
     </row>
     <row r="98">
@@ -20497,17 +20939,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>7514.85</v>
+        <v>32984.2</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>11735.52</v>
+        <v>34707.86</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>1561.643944988922</v>
+        <v>1052.257141297955</v>
       </c>
     </row>
     <row r="99">
@@ -20518,17 +20960,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>2</v>
+        <v>10982.17</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>3.57</v>
+        <v>17973.24</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>1785</v>
+        <v>1636.583662427371</v>
       </c>
     </row>
     <row r="100">
@@ -20539,17 +20981,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>12070.4</v>
+        <v>8497.539999999999</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>14391.17</v>
+        <v>13331.46</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1192.269518822905</v>
+        <v>1568.861105684704</v>
       </c>
     </row>
     <row r="101">
@@ -20560,17 +21002,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>0.24</v>
+        <v>3.57</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>4800</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="102">
@@ -20581,17 +21023,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>653.25</v>
+        <v>12031.83</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>636.14</v>
+        <v>14194.2</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>973.80788365863</v>
+        <v>1179.720790602925</v>
       </c>
     </row>
     <row r="103">
@@ -20602,17 +21044,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>20116.69</v>
+        <v>0.05</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>18313.92</v>
+        <v>0.24</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>910.3843624373593</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="104">
@@ -20623,17 +21065,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>637.12</v>
+        <v>653.25</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>972.5999999999999</v>
+        <v>636.14</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>1526.557006529382</v>
+        <v>973.80788365863</v>
       </c>
     </row>
     <row r="105">
@@ -20644,17 +21086,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>328.6</v>
+        <v>20116.69</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>437.03</v>
+        <v>18313.92</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>1329.975654290932</v>
+        <v>910.3843624373593</v>
       </c>
     </row>
     <row r="106">
@@ -20665,17 +21107,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>74686.57000000001</v>
+        <v>637.12</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>18004.27</v>
+        <v>972.5999999999999</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>241.0643573536715</v>
+        <v>1526.557006529382</v>
       </c>
     </row>
     <row r="107">
@@ -20686,16 +21128,58 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>328.9</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>438.0000000000001</v>
+      </c>
+      <c r="E107" s="6" t="n">
+        <v>1331.711766494376</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>8429.839999999997</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>21945.02</v>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>2603.254628794853</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="C107" s="6" t="n">
+      <c r="C109" s="6" t="n">
         <v>690.49</v>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D109" s="6" t="n">
         <v>579.4100000000001</v>
       </c>
-      <c r="E107" s="6" t="n">
+      <c r="E109" s="6" t="n">
         <v>839.1287346666861</v>
       </c>
     </row>

--- a/data/canada_trq_tracker.xlsx
+++ b/data/canada_trq_tracker.xlsx
@@ -12390,7 +12390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12481,7 +12481,12 @@
           <t>September 14 2026</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>September 21 2026</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
@@ -12540,6 +12545,9 @@
       <c r="Q3" s="4" t="n">
         <v>0.3369</v>
       </c>
+      <c r="R3" s="4" t="n">
+        <v>0.3369</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12591,6 +12599,9 @@
       <c r="Q4" s="4" t="n">
         <v>0.0396</v>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>0.0436</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12636,6 +12647,9 @@
       <c r="Q5" s="4" t="n">
         <v>0.0009</v>
       </c>
+      <c r="R5" s="4" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12700,6 +12714,10 @@
         <f>SUM(Q3:Q5)</f>
         <v/>
       </c>
+      <c r="R6" s="5">
+        <f>SUM(R3:R5)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12754,6 +12772,9 @@
       <c r="Q7" s="4" t="n">
         <v>0.3542</v>
       </c>
+      <c r="R7" s="4" t="n">
+        <v>0.3542</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12802,6 +12823,9 @@
       <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12829,6 +12853,9 @@
       <c r="Q9" s="4" t="n">
         <v>0.3547</v>
       </c>
+      <c r="R9" s="4" t="n">
+        <v>0.3547</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12871,6 +12898,9 @@
       <c r="Q11" s="4" t="n">
         <v>0.1897</v>
       </c>
+      <c r="R11" s="4" t="n">
+        <v>0.2734</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12935,6 +12965,10 @@
         <f>SUM(Q7:Q11)</f>
         <v/>
       </c>
+      <c r="R12" s="5">
+        <f>SUM(R7:R11)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12989,6 +13023,9 @@
       <c r="Q13" s="4" t="n">
         <v>0.001</v>
       </c>
+      <c r="R13" s="4" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13043,6 +13080,9 @@
       <c r="Q14" s="4" t="n">
         <v>0.1135</v>
       </c>
+      <c r="R14" s="4" t="n">
+        <v>0.1135</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13097,6 +13137,9 @@
       <c r="Q15" s="4" t="n">
         <v>0.5222</v>
       </c>
+      <c r="R15" s="4" t="n">
+        <v>0.5222</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13148,6 +13191,9 @@
       <c r="Q16" s="4" t="n">
         <v>0.0008</v>
       </c>
+      <c r="R16" s="4" t="n">
+        <v>0.0008</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13199,6 +13245,9 @@
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13250,6 +13299,9 @@
       <c r="Q18" s="4" t="n">
         <v>0.3156</v>
       </c>
+      <c r="R18" s="4" t="n">
+        <v>0.3156</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13298,6 +13350,9 @@
       <c r="Q19" s="4" t="n">
         <v>0.0406</v>
       </c>
+      <c r="R19" s="4" t="n">
+        <v>0.0406</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13346,6 +13401,9 @@
       <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13410,6 +13468,10 @@
         <f>SUM(Q13:Q20)</f>
         <v/>
       </c>
+      <c r="R21" s="5">
+        <f>SUM(R13:R20)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13464,6 +13526,9 @@
       <c r="Q22" s="4" t="n">
         <v>0.003</v>
       </c>
+      <c r="R22" s="4" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13518,6 +13583,9 @@
       <c r="Q23" s="4" t="n">
         <v>0.2673</v>
       </c>
+      <c r="R23" s="4" t="n">
+        <v>0.2673</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13572,6 +13640,9 @@
       <c r="Q24" s="4" t="n">
         <v>0.0069</v>
       </c>
+      <c r="R24" s="4" t="n">
+        <v>0.0069</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13626,6 +13697,9 @@
       <c r="Q25" s="4" t="n">
         <v>0.2488</v>
       </c>
+      <c r="R25" s="4" t="n">
+        <v>0.2488</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13680,6 +13754,9 @@
       <c r="Q26" s="4" t="n">
         <v>0.3697</v>
       </c>
+      <c r="R26" s="4" t="n">
+        <v>0.3697</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13734,6 +13811,9 @@
       <c r="Q27" s="4" t="n">
         <v>0.0289</v>
       </c>
+      <c r="R27" s="4" t="n">
+        <v>0.0289</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13785,6 +13865,9 @@
       <c r="Q28" s="4" t="n">
         <v>0.07539999999999999</v>
       </c>
+      <c r="R28" s="4" t="n">
+        <v>0.07539999999999999</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13849,6 +13932,10 @@
         <f>SUM(Q22:Q28)</f>
         <v/>
       </c>
+      <c r="R29" s="5">
+        <f>SUM(R22:R28)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13903,7 +13990,10 @@
       <c r="Q30" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R30" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -13962,6 +14052,9 @@
       <c r="Q31" s="4" t="n">
         <v>0.0037</v>
       </c>
+      <c r="R31" s="4" t="n">
+        <v>0.0037</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14016,6 +14109,9 @@
       <c r="Q32" s="4" t="n">
         <v>0.2899</v>
       </c>
+      <c r="R32" s="4" t="n">
+        <v>0.2899</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -14070,6 +14166,9 @@
       <c r="Q33" s="4" t="n">
         <v>0.0883</v>
       </c>
+      <c r="R33" s="4" t="n">
+        <v>0.0883</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -14115,6 +14214,9 @@
       <c r="Q34" s="4" t="n">
         <v>0.0113</v>
       </c>
+      <c r="R34" s="4" t="n">
+        <v>0.0113</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14139,6 +14241,9 @@
       <c r="Q35" s="4" t="n">
         <v>0.2822</v>
       </c>
+      <c r="R35" s="4" t="n">
+        <v>0.2822</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14203,6 +14308,10 @@
         <f>SUM(Q30:Q35)</f>
         <v/>
       </c>
+      <c r="R36" s="5">
+        <f>SUM(R30:R35)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -14257,6 +14366,9 @@
       <c r="Q37" s="4" t="n">
         <v>0.1576</v>
       </c>
+      <c r="R37" s="4" t="n">
+        <v>0.1576</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -14311,7 +14423,10 @@
       <c r="Q38" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R38" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -14370,7 +14485,10 @@
       <c r="Q39" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -14426,6 +14544,9 @@
       <c r="Q40" s="4" t="n">
         <v>0.0024</v>
       </c>
+      <c r="R40" s="4" t="n">
+        <v>0.0024</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14490,6 +14611,10 @@
         <f>SUM(Q37:Q40)</f>
         <v/>
       </c>
+      <c r="R41" s="5">
+        <f>SUM(R37:R40)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14532,6 +14657,14 @@
       <c r="Q42" s="4" t="n">
         <v>0.4069</v>
       </c>
+      <c r="R42" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14571,7 +14704,10 @@
       <c r="Q43" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -14640,6 +14776,10 @@
         <f>SUM(Q42:Q43)</f>
         <v/>
       </c>
+      <c r="R44" s="5">
+        <f>SUM(R42:R43)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14694,6 +14834,9 @@
       <c r="Q45" s="4" t="n">
         <v>0.0146</v>
       </c>
+      <c r="R45" s="4" t="n">
+        <v>0.0146</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14748,6 +14891,9 @@
       <c r="Q46" s="4" t="n">
         <v>0.2065</v>
       </c>
+      <c r="R46" s="4" t="n">
+        <v>0.2065</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14802,6 +14948,9 @@
       <c r="Q47" s="4" t="n">
         <v>0.3483</v>
       </c>
+      <c r="R47" s="4" t="n">
+        <v>0.3483</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14856,6 +15005,9 @@
       <c r="Q48" s="4" t="n">
         <v>0.4306</v>
       </c>
+      <c r="R48" s="4" t="n">
+        <v>0.4306</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14918,6 +15070,10 @@
       </c>
       <c r="Q49" s="5">
         <f>SUM(Q45:Q48)</f>
+        <v/>
+      </c>
+      <c r="R49" s="5">
+        <f>SUM(R45:R48)</f>
         <v/>
       </c>
     </row>
@@ -14932,7 +15088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R80"/>
+  <dimension ref="A1:S80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15023,7 +15179,12 @@
           <t>September 14 2026</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>September 21 2026</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
@@ -15082,6 +15243,9 @@
       <c r="Q3" s="4" t="n">
         <v>0.3165</v>
       </c>
+      <c r="R3" s="4" t="n">
+        <v>0.3165</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15136,6 +15300,9 @@
       <c r="Q4" s="4" t="n">
         <v>0.6835</v>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>0.6835</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15200,6 +15367,10 @@
         <f>SUM(Q3:Q4)</f>
         <v/>
       </c>
+      <c r="R5" s="5">
+        <f>SUM(R3:R4)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15254,6 +15425,9 @@
       <c r="Q6" s="4" t="n">
         <v>0.0452</v>
       </c>
+      <c r="R6" s="4" t="n">
+        <v>0.0452</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15308,6 +15482,9 @@
       <c r="Q7" s="4" t="n">
         <v>0.0261</v>
       </c>
+      <c r="R7" s="4" t="n">
+        <v>0.0261</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15362,6 +15539,9 @@
       <c r="Q8" s="4" t="n">
         <v>0.0009</v>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>0.0009</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15416,6 +15596,9 @@
       <c r="Q9" s="4" t="n">
         <v>0.0142</v>
       </c>
+      <c r="R9" s="4" t="n">
+        <v>0.0142</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15470,6 +15653,9 @@
       <c r="Q10" s="4" t="n">
         <v>0.2225</v>
       </c>
+      <c r="R10" s="4" t="n">
+        <v>0.2225</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15524,6 +15710,9 @@
       <c r="Q11" s="4" t="n">
         <v>0.2101</v>
       </c>
+      <c r="R11" s="4" t="n">
+        <v>0.2101</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15578,6 +15767,9 @@
       <c r="Q12" s="4" t="n">
         <v>0.08310000000000001</v>
       </c>
+      <c r="R12" s="4" t="n">
+        <v>0.08310000000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15632,7 +15824,10 @@
       <c r="Q13" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R13" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -15691,6 +15886,9 @@
       <c r="Q14" s="4" t="n">
         <v>0.001</v>
       </c>
+      <c r="R14" s="4" t="n">
+        <v>0.001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15745,6 +15943,9 @@
       <c r="Q15" s="4" t="n">
         <v>0.0624</v>
       </c>
+      <c r="R15" s="4" t="n">
+        <v>0.0624</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15796,6 +15997,9 @@
       <c r="Q16" s="4" t="n">
         <v>0.0013</v>
       </c>
+      <c r="R16" s="4" t="n">
+        <v>0.0013</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15860,6 +16064,10 @@
         <f>SUM(Q6:Q16)</f>
         <v/>
       </c>
+      <c r="R17" s="5">
+        <f>SUM(R6:R16)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15914,6 +16122,9 @@
       <c r="Q18" s="4" t="n">
         <v>0.0276</v>
       </c>
+      <c r="R18" s="4" t="n">
+        <v>0.0276</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15968,6 +16179,9 @@
       <c r="Q19" s="4" t="n">
         <v>0.2141</v>
       </c>
+      <c r="R19" s="4" t="n">
+        <v>0.2157</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16022,6 +16236,9 @@
       <c r="Q20" s="4" t="n">
         <v>0.0175</v>
       </c>
+      <c r="R20" s="4" t="n">
+        <v>0.0175</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16073,7 +16290,10 @@
       <c r="Q21" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -16114,6 +16334,9 @@
       <c r="Q22" s="4" t="n">
         <v>0.0043</v>
       </c>
+      <c r="R22" s="4" t="n">
+        <v>0.0043</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16144,6 +16367,9 @@
       <c r="Q23" s="4" t="n">
         <v>0.0086</v>
       </c>
+      <c r="R23" s="4" t="n">
+        <v>0.0167</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16168,6 +16394,9 @@
       <c r="Q24" s="4" t="n">
         <v>0.006</v>
       </c>
+      <c r="R24" s="4" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16232,6 +16461,10 @@
         <f>SUM(Q18:Q24)</f>
         <v/>
       </c>
+      <c r="R25" s="5">
+        <f>SUM(R18:R24)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16286,6 +16519,9 @@
       <c r="Q26" s="4" t="n">
         <v>0.2462</v>
       </c>
+      <c r="R26" s="4" t="n">
+        <v>0.2462</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16340,6 +16576,9 @@
       <c r="Q27" s="4" t="n">
         <v>0.08960000000000001</v>
       </c>
+      <c r="R27" s="4" t="n">
+        <v>0.08960000000000001</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16394,7 +16633,10 @@
       <c r="Q28" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -16453,6 +16695,9 @@
       <c r="Q29" s="4" t="n">
         <v>0.04940000000000001</v>
       </c>
+      <c r="R29" s="4" t="n">
+        <v>0.04940000000000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16507,6 +16752,9 @@
       <c r="Q30" s="4" t="n">
         <v>0.0533</v>
       </c>
+      <c r="R30" s="4" t="n">
+        <v>0.0533</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16561,6 +16809,9 @@
       <c r="Q31" s="4" t="n">
         <v>0.1124</v>
       </c>
+      <c r="R31" s="4" t="n">
+        <v>0.1124</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16612,6 +16863,9 @@
       <c r="Q32" s="4" t="n">
         <v>0.1044</v>
       </c>
+      <c r="R32" s="4" t="n">
+        <v>0.1044</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16663,6 +16917,9 @@
       <c r="Q33" s="4" t="n">
         <v>0.0226</v>
       </c>
+      <c r="R33" s="4" t="n">
+        <v>0.0226</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16714,6 +16971,9 @@
       <c r="Q34" s="4" t="n">
         <v>0.0369</v>
       </c>
+      <c r="R34" s="4" t="n">
+        <v>0.0369</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16762,6 +17022,9 @@
       <c r="Q35" s="4" t="n">
         <v>0.0014</v>
       </c>
+      <c r="R35" s="4" t="n">
+        <v>0.0014</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16801,6 +17064,9 @@
       <c r="Q36" s="4" t="n">
         <v>0.0273</v>
       </c>
+      <c r="R36" s="4" t="n">
+        <v>0.0273</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16831,6 +17097,9 @@
       <c r="Q37" s="4" t="n">
         <v>0.0027</v>
       </c>
+      <c r="R37" s="4" t="n">
+        <v>0.0027</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16861,6 +17130,9 @@
       <c r="Q38" s="4" t="n">
         <v>0.0002</v>
       </c>
+      <c r="R38" s="4" t="n">
+        <v>0.0002</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16888,6 +17160,9 @@
       <c r="Q39" s="4" t="n">
         <v>0.0005999999999999999</v>
       </c>
+      <c r="R39" s="4" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16952,6 +17227,10 @@
         <f>SUM(Q26:Q39)</f>
         <v/>
       </c>
+      <c r="R40" s="5">
+        <f>SUM(R26:R39)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17006,6 +17285,9 @@
       <c r="Q41" s="4" t="n">
         <v>0.2142</v>
       </c>
+      <c r="R41" s="4" t="n">
+        <v>0.2142</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -17060,6 +17342,9 @@
       <c r="Q42" s="4" t="n">
         <v>0.3459</v>
       </c>
+      <c r="R42" s="4" t="n">
+        <v>0.3459</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -17111,6 +17396,9 @@
       <c r="Q43" s="4" t="n">
         <v>0.0007000000000000001</v>
       </c>
+      <c r="R43" s="4" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -17150,6 +17438,9 @@
       <c r="Q44" s="4" t="n">
         <v>0.4389</v>
       </c>
+      <c r="R44" s="4" t="n">
+        <v>0.4389</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17174,6 +17465,9 @@
       <c r="Q45" s="4" t="n">
         <v>0.0003</v>
       </c>
+      <c r="R45" s="4" t="n">
+        <v>0.0003</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -17238,6 +17532,10 @@
         <f>SUM(Q41:Q45)</f>
         <v/>
       </c>
+      <c r="R46" s="5">
+        <f>SUM(R41:R45)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17292,6 +17590,9 @@
       <c r="Q47" s="4" t="n">
         <v>0.0025</v>
       </c>
+      <c r="R47" s="4" t="n">
+        <v>0.0025</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -17346,6 +17647,9 @@
       <c r="Q48" s="4" t="n">
         <v>0.4215</v>
       </c>
+      <c r="R48" s="4" t="n">
+        <v>0.4215</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17400,6 +17704,9 @@
       <c r="Q49" s="4" t="n">
         <v>0.1712</v>
       </c>
+      <c r="R49" s="4" t="n">
+        <v>0.1712</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17454,6 +17761,9 @@
       <c r="Q50" s="4" t="n">
         <v>0.016</v>
       </c>
+      <c r="R50" s="4" t="n">
+        <v>0.016</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17508,6 +17818,9 @@
       <c r="Q51" s="4" t="n">
         <v>0.0133</v>
       </c>
+      <c r="R51" s="4" t="n">
+        <v>0.0133</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17562,6 +17875,9 @@
       <c r="Q52" s="4" t="n">
         <v>0.0708</v>
       </c>
+      <c r="R52" s="4" t="n">
+        <v>0.0708</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17613,6 +17929,9 @@
       <c r="Q53" s="4" t="n">
         <v>0.0072</v>
       </c>
+      <c r="R53" s="4" t="n">
+        <v>0.0095</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17664,6 +17983,9 @@
       <c r="Q54" s="4" t="n">
         <v>0.2923</v>
       </c>
+      <c r="R54" s="4" t="n">
+        <v>0.2923</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17712,6 +18034,9 @@
       <c r="Q55" s="4" t="n">
         <v>0.0001</v>
       </c>
+      <c r="R55" s="4" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17760,6 +18085,9 @@
       <c r="Q56" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R56" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17808,6 +18136,9 @@
       <c r="Q57" s="4" t="n">
         <v>0.0022</v>
       </c>
+      <c r="R57" s="4" t="n">
+        <v>0.0022</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17856,6 +18187,9 @@
       <c r="Q58" s="4" t="n">
         <v>0.0004</v>
       </c>
+      <c r="R58" s="4" t="n">
+        <v>0.0004</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17904,6 +18238,9 @@
       <c r="Q59" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R59" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17949,6 +18286,9 @@
       <c r="Q60" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R60" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17994,6 +18334,9 @@
       <c r="Q61" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R61" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -18036,6 +18379,9 @@
       <c r="Q62" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R62" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -18075,6 +18421,9 @@
       <c r="Q63" s="4" t="n">
         <v>0.0001</v>
       </c>
+      <c r="R63" s="4" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -18139,6 +18488,10 @@
         <f>SUM(Q47:Q63)</f>
         <v/>
       </c>
+      <c r="R64" s="5">
+        <f>SUM(R47:R63)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -18193,6 +18546,9 @@
       <c r="Q65" s="4" t="n">
         <v>0.3348</v>
       </c>
+      <c r="R65" s="4" t="n">
+        <v>0.3361</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18247,6 +18603,9 @@
       <c r="Q66" s="4" t="n">
         <v>0.0698</v>
       </c>
+      <c r="R66" s="4" t="n">
+        <v>0.0698</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18301,6 +18660,9 @@
       <c r="Q67" s="4" t="n">
         <v>0.4926</v>
       </c>
+      <c r="R67" s="4" t="n">
+        <v>0.4926</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18355,6 +18717,9 @@
       <c r="Q68" s="4" t="n">
         <v>0.0293</v>
       </c>
+      <c r="R68" s="4" t="n">
+        <v>0.0293</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18403,6 +18768,9 @@
       <c r="Q69" s="4" t="n">
         <v>0.008500000000000001</v>
       </c>
+      <c r="R69" s="4" t="n">
+        <v>0.008500000000000001</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18436,6 +18804,9 @@
       <c r="Q70" s="4" t="n">
         <v>0.0022</v>
       </c>
+      <c r="R70" s="4" t="n">
+        <v>0.0022</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18500,6 +18871,10 @@
         <f>SUM(Q65:Q70)</f>
         <v/>
       </c>
+      <c r="R71" s="5">
+        <f>SUM(R65:R70)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18554,6 +18929,9 @@
       <c r="Q72" s="4" t="n">
         <v>0.0021</v>
       </c>
+      <c r="R72" s="4" t="n">
+        <v>0.0021</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18608,6 +18986,9 @@
       <c r="Q73" s="4" t="n">
         <v>0.0032</v>
       </c>
+      <c r="R73" s="4" t="n">
+        <v>0.0032</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18662,6 +19043,9 @@
       <c r="Q74" s="4" t="n">
         <v>0.0204</v>
       </c>
+      <c r="R74" s="4" t="n">
+        <v>0.0204</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18716,7 +19100,10 @@
       <c r="Q75" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="R75" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="S75" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
@@ -18775,6 +19162,9 @@
       <c r="Q76" s="4" t="n">
         <v>0.0004</v>
       </c>
+      <c r="R76" s="4" t="n">
+        <v>0.0004</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18829,6 +19219,9 @@
       <c r="Q77" s="4" t="n">
         <v>0.2828</v>
       </c>
+      <c r="R77" s="4" t="n">
+        <v>0.2828</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18880,6 +19273,9 @@
       <c r="Q78" s="4" t="n">
         <v>0.0012</v>
       </c>
+      <c r="R78" s="4" t="n">
+        <v>0.0012</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18928,6 +19324,9 @@
       <c r="Q79" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R79" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18990,6 +19389,10 @@
       </c>
       <c r="Q80" s="5">
         <f>SUM(Q72:Q79)</f>
+        <v/>
+      </c>
+      <c r="R80" s="5">
+        <f>SUM(R72:R79)</f>
         <v/>
       </c>
     </row>
@@ -19004,7 +19407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19116,13 +19519,13 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>28</v>
+        <v>28.03</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8.27</v>
+        <v>24.8</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>295.3571428571428</v>
+        <v>884.7663217980735</v>
       </c>
     </row>
     <row r="12">
@@ -19263,13 +19666,13 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>14409.51</v>
+        <v>16497.85</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>25027</v>
+        <v>28780.17</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1736.839073639562</v>
+        <v>1744.480038308022</v>
       </c>
     </row>
     <row r="19">
@@ -19347,13 +19750,13 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>971.6500000000001</v>
+        <v>1124.85</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4207.960000000001</v>
+        <v>4886.18</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4330.736376267175</v>
+        <v>4343.850291149932</v>
       </c>
     </row>
     <row r="23">
@@ -19452,13 +19855,13 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>70.61999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>176.62</v>
+        <v>195.69</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>2500.991220617389</v>
+        <v>2448.573573573573</v>
       </c>
     </row>
     <row r="28">
@@ -19515,13 +19918,13 @@
         </is>
       </c>
       <c r="C30" s="6" t="n">
-        <v>9083.459999999999</v>
+        <v>10517.34999999999</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>20469.96</v>
+        <v>23896.71000000001</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2253.542152439709</v>
+        <v>2272.122730535736</v>
       </c>
     </row>
     <row r="31">
@@ -19536,13 +19939,13 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>36.85999999999999</v>
+        <v>37.89999999999999</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>84.98</v>
+        <v>86.98</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>2305.480195333696</v>
+        <v>2294.986807387863</v>
       </c>
     </row>
     <row r="32">
@@ -19620,13 +20023,13 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>424.12</v>
+        <v>492.18</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>761.33</v>
+        <v>817.4100000000001</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>1795.081580684712</v>
+        <v>1660.794831159332</v>
       </c>
     </row>
     <row r="36">
@@ -19704,13 +20107,13 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>11411.46</v>
+        <v>12738.41</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>21267.10999999999</v>
+        <v>23782.68</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>1863.662493668645</v>
+        <v>1867.005379792298</v>
       </c>
     </row>
     <row r="40">
@@ -19725,13 +20128,13 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>6722.290000000001</v>
+        <v>7213.89</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>7449.77</v>
+        <v>8054.110000000001</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1108.219074154789</v>
+        <v>1116.472527304963</v>
       </c>
     </row>
     <row r="41">
@@ -19767,13 +20170,13 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1795.37</v>
+        <v>1868.6</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>2421.72</v>
+        <v>2475.41</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>1348.869592340298</v>
+        <v>1324.740447393771</v>
       </c>
     </row>
     <row r="43">
@@ -19809,13 +20212,13 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>4841.26</v>
+        <v>4921.71</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>9501.809999999999</v>
+        <v>9661.15</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1962.672940515486</v>
+        <v>1962.966123562745</v>
       </c>
     </row>
     <row r="45">
@@ -19893,13 +20296,13 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>17416.15</v>
+        <v>17430.11</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>28775.74</v>
+        <v>28817.23</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1652.244612041122</v>
+        <v>1653.301671647512</v>
       </c>
     </row>
     <row r="49">
@@ -19910,17 +20313,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>663.12</v>
+        <v>84.97</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1537.45</v>
+        <v>96.47</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>2318.509470382435</v>
+        <v>1135.341885371308</v>
       </c>
     </row>
     <row r="50">
@@ -19931,17 +20334,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>85.22</v>
+        <v>829.95</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>144.14</v>
+        <v>1926.96</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1691.386998357193</v>
+        <v>2321.77842038677</v>
       </c>
     </row>
     <row r="51">
@@ -19952,17 +20355,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>488.37</v>
+        <v>85.22</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>940.9100000000001</v>
+        <v>144.14</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>1926.633495095931</v>
+        <v>1691.386998357193</v>
       </c>
     </row>
     <row r="52">
@@ -19973,17 +20376,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>4562.59</v>
+        <v>488.37</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>5650.14</v>
+        <v>940.9100000000001</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1238.362421344017</v>
+        <v>1926.633495095931</v>
       </c>
     </row>
     <row r="53">
@@ -19994,17 +20397,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>5.02</v>
+        <v>4689.37</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>24.36</v>
+        <v>5821.76</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>4852.589641434263</v>
+        <v>1241.480198832679</v>
       </c>
     </row>
     <row r="54">
@@ -20015,17 +20418,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
-        <v>455.09</v>
+        <v>5.02</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>644.63</v>
+        <v>24.36</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1416.489046122745</v>
+        <v>4852.589641434263</v>
       </c>
     </row>
     <row r="55">
@@ -20036,17 +20439,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>0.01</v>
+        <v>455.09</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.03</v>
+        <v>644.63</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>3000</v>
+        <v>1416.489046122745</v>
       </c>
     </row>
     <row r="56">
@@ -20057,17 +20460,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>2083.333333333333</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="57">
@@ -20078,17 +20481,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>7295.74</v>
+        <v>0.12</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>11154.6</v>
+        <v>0.25</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>1528.91961610474</v>
+        <v>2083.333333333333</v>
       </c>
     </row>
     <row r="58">
@@ -20099,17 +20502,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>542.15</v>
+        <v>12664.74</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>737.62</v>
+        <v>17203.03</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1360.545974361339</v>
+        <v>1358.340558116471</v>
       </c>
     </row>
     <row r="59">
@@ -20120,17 +20523,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
-        <v>3687.78</v>
+        <v>542.15</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>4387.33</v>
+        <v>737.62</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>1189.694070687514</v>
+        <v>1360.545974361339</v>
       </c>
     </row>
     <row r="60">
@@ -20141,17 +20544,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C60" s="6" t="n">
-        <v>0.33</v>
+        <v>3687.78</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>1.37</v>
+        <v>4387.33</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>4151.515151515151</v>
+        <v>1189.694070687514</v>
       </c>
     </row>
     <row r="61">
@@ -20162,17 +20565,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>15.63</v>
+        <v>0.33</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>45.93</v>
+        <v>1.37</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>2938.579654510556</v>
+        <v>4151.515151515151</v>
       </c>
     </row>
     <row r="62">
@@ -20183,17 +20586,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C62" s="6" t="n">
-        <v>35556.35999999999</v>
+        <v>15.63</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>75316.79000000001</v>
+        <v>45.93</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>2118.236793642545</v>
+        <v>2938.579654510556</v>
       </c>
     </row>
     <row r="63">
@@ -20204,38 +20607,38 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>1988.28</v>
+        <v>39172.45</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2548.99</v>
+        <v>83093.71000000005</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>1282.007564326956</v>
+        <v>2121.228312244959</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rebar</t>
+          <t>Coated Steel Sheet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>133.1</v>
+        <v>1988.28</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>169.14</v>
+        <v>2548.99</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>1270.773854244928</v>
+        <v>1282.007564326956</v>
       </c>
     </row>
     <row r="65">
@@ -20246,17 +20649,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
-        <v>19.72</v>
+        <v>133.1</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>39.63</v>
+        <v>169.14</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>2009.634888438134</v>
+        <v>1270.773854244928</v>
       </c>
     </row>
     <row r="66">
@@ -20267,17 +20670,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>7.31</v>
+        <v>19.72</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>19.98</v>
+        <v>39.63</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>2733.242134062928</v>
+        <v>2009.634888438134</v>
       </c>
     </row>
     <row r="67">
@@ -20288,17 +20691,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>2066.03</v>
+        <v>7.31</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>1573.68</v>
+        <v>19.98</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>761.6927150138189</v>
+        <v>2733.242134062928</v>
       </c>
     </row>
     <row r="68">
@@ -20309,17 +20712,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>9921.959999999999</v>
+        <v>2066.03</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>7484.200000000001</v>
+        <v>1573.68</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>754.3066087748794</v>
+        <v>761.6927150138189</v>
       </c>
     </row>
     <row r="69">
@@ -20330,17 +20733,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
-        <v>9048.489999999998</v>
+        <v>9921.959999999999</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>12398.53</v>
+        <v>7484.200000000001</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1370.231939251743</v>
+        <v>754.3066087748794</v>
       </c>
     </row>
     <row r="70">
@@ -20351,17 +20754,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>49.88</v>
+        <v>9299.099999999999</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>80.97</v>
+        <v>12734.46</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1623.295910184443</v>
+        <v>1369.42929960964</v>
       </c>
     </row>
     <row r="71">
@@ -20372,38 +20775,38 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>504.5500000000001</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>739.8299999999999</v>
+        <v>155.63</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>1466.316519670994</v>
+        <v>1560.04410585405</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hot-Rolled Bar</t>
+          <t>Rebar</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>166.21</v>
+        <v>605.9400000000001</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>362.5</v>
+        <v>874.8</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>2180.975873894471</v>
+        <v>1443.707297752253</v>
       </c>
     </row>
     <row r="73">
@@ -20414,17 +20817,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>28.89</v>
+        <v>173.57</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>51.74</v>
+        <v>378.35</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1790.931118033922</v>
+        <v>2179.812179524111</v>
       </c>
     </row>
     <row r="74">
@@ -20435,17 +20838,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
-        <v>645.63</v>
+        <v>200.14</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>1079.21</v>
+        <v>266.08</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1671.561110852965</v>
+        <v>1329.469371439992</v>
       </c>
     </row>
     <row r="75">
@@ -20456,17 +20859,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
-        <v>0.01</v>
+        <v>645.63</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>0.01</v>
+        <v>1079.21</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>1000</v>
+        <v>1671.561110852965</v>
       </c>
     </row>
     <row r="76">
@@ -20477,17 +20880,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>680.04</v>
+        <v>0.01</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>1020.66</v>
+        <v>0.01</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1500.882301041115</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="77">
@@ -20498,17 +20901,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>63.19</v>
+        <v>3.95</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>133.25</v>
+        <v>16.83</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>2108.719734135148</v>
+        <v>4260.759493670886</v>
       </c>
     </row>
     <row r="78">
@@ -20519,17 +20922,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
-        <v>2231.47</v>
+        <v>880</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>2253.41</v>
+        <v>1374.45</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>1009.832083783336</v>
+        <v>1561.875</v>
       </c>
     </row>
     <row r="79">
@@ -20540,17 +20943,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>321.41</v>
+        <v>63.19</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>335.59</v>
+        <v>133.25</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>1044.118104601599</v>
+        <v>2108.719734135148</v>
       </c>
     </row>
     <row r="80">
@@ -20561,59 +20964,59 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
-        <v>2987</v>
+        <v>2398.91</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>6399.969999999999</v>
+        <v>2434.17</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>2142.607967860729</v>
+        <v>1014.698342163733</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
-        <v>72.08</v>
+        <v>321.41</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>104.06</v>
+        <v>335.59</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>1443.673695893452</v>
+        <v>1044.118104601599</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Wire Rod</t>
+          <t>Hot-Rolled Bar</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>385.82</v>
+        <v>3363.5</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>496.14</v>
+        <v>7237.199999999998</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>1285.936447047846</v>
+        <v>2151.687230563401</v>
       </c>
     </row>
     <row r="83">
@@ -20624,17 +21027,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C83" s="6" t="n">
-        <v>5714.400000000001</v>
+        <v>72.08</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>7504.52</v>
+        <v>104.06</v>
       </c>
       <c r="E83" s="6" t="n">
-        <v>1313.264734705306</v>
+        <v>1443.673695893452</v>
       </c>
     </row>
     <row r="84">
@@ -20645,17 +21048,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>1.83</v>
+        <v>745.3499999999999</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>5.66</v>
+        <v>1002.02</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>3092.896174863388</v>
+        <v>1344.361709264104</v>
       </c>
     </row>
     <row r="85">
@@ -20666,17 +21069,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>88.08000000000001</v>
+        <v>6480.490000000001</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>147.89</v>
+        <v>8480.98</v>
       </c>
       <c r="E85" s="6" t="n">
-        <v>1679.041780199818</v>
+        <v>1308.694249971838</v>
       </c>
     </row>
     <row r="86">
@@ -20687,17 +21090,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>2679.14</v>
+        <v>1.83</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>2208.72</v>
+        <v>5.66</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>824.4138044297797</v>
+        <v>3092.896174863388</v>
       </c>
     </row>
     <row r="87">
@@ -20708,17 +21111,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C87" s="6" t="n">
-        <v>95.56999999999999</v>
+        <v>88.08000000000001</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>256.16</v>
+        <v>147.89</v>
       </c>
       <c r="E87" s="6" t="n">
-        <v>2680.339018520457</v>
+        <v>1679.041780199818</v>
       </c>
     </row>
     <row r="88">
@@ -20729,17 +21132,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>193.25</v>
+        <v>2679.14</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>263.71</v>
+        <v>2208.72</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>1364.605433376456</v>
+        <v>824.4138044297797</v>
       </c>
     </row>
     <row r="89">
@@ -20750,17 +21153,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C89" s="6" t="n">
-        <v>93.3</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>138.03</v>
+        <v>256.16</v>
       </c>
       <c r="E89" s="6" t="n">
-        <v>1479.421221864952</v>
+        <v>2680.339018520457</v>
       </c>
     </row>
     <row r="90">
@@ -20771,17 +21174,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C90" s="6" t="n">
-        <v>297.7</v>
+        <v>193.25</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>389.33</v>
+        <v>263.71</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>1307.793080282163</v>
+        <v>1364.605433376456</v>
       </c>
     </row>
     <row r="91">
@@ -20792,59 +21195,59 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>7342.349999999999</v>
+        <v>93.3</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>11178.65</v>
+        <v>138.03</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>1522.489393722719</v>
+        <v>1479.421221864952</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>2420.79</v>
+        <v>297.7</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>2123.93</v>
+        <v>389.33</v>
       </c>
       <c r="E92" s="6" t="n">
-        <v>877.3706104205654</v>
+        <v>1307.793080282163</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Structural Steel</t>
+          <t>Wire Rod</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>1.15</v>
+        <v>8103.02</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>2.14</v>
+        <v>12269.07</v>
       </c>
       <c r="E93" s="6" t="n">
-        <v>1860.869565217391</v>
+        <v>1514.135470478908</v>
       </c>
     </row>
     <row r="94">
@@ -20855,17 +21258,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>388.01</v>
+        <v>2420.79</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1254.6</v>
+        <v>2123.93</v>
       </c>
       <c r="E94" s="6" t="n">
-        <v>3233.421819025283</v>
+        <v>877.3706104205654</v>
       </c>
     </row>
     <row r="95">
@@ -20876,17 +21279,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C95" s="6" t="n">
-        <v>55.54</v>
+        <v>1.15</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>81.45</v>
+        <v>2.14</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>1466.510622974433</v>
+        <v>1860.869565217391</v>
       </c>
     </row>
     <row r="96">
@@ -20897,17 +21300,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C96" s="6" t="n">
-        <v>17.16</v>
+        <v>388.11</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>80.98999999999999</v>
+        <v>1255.37</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>4719.69696969697</v>
+        <v>3234.572672695885</v>
       </c>
     </row>
     <row r="97">
@@ -20918,17 +21321,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C97" s="6" t="n">
-        <v>824.29</v>
+        <v>55.54</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>926.6900000000001</v>
+        <v>81.45</v>
       </c>
       <c r="E97" s="6" t="n">
-        <v>1124.228123597278</v>
+        <v>1466.510622974433</v>
       </c>
     </row>
     <row r="98">
@@ -20939,17 +21342,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Korea, Republic of</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>32984.2</v>
+        <v>18</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>34707.86</v>
+        <v>85.08</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>1052.257141297955</v>
+        <v>4726.666666666668</v>
       </c>
     </row>
     <row r="99">
@@ -20960,17 +21363,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C99" s="6" t="n">
-        <v>10982.17</v>
+        <v>824.29</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>17973.24</v>
+        <v>926.6900000000001</v>
       </c>
       <c r="E99" s="6" t="n">
-        <v>1636.583662427371</v>
+        <v>1124.228123597278</v>
       </c>
     </row>
     <row r="100">
@@ -20981,17 +21384,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Korea, Republic of</t>
         </is>
       </c>
       <c r="C100" s="6" t="n">
-        <v>8497.539999999999</v>
+        <v>32984.2</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>13331.46</v>
+        <v>34707.86</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1568.861105684704</v>
+        <v>1052.257141297955</v>
       </c>
     </row>
     <row r="101">
@@ -21002,17 +21405,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C101" s="6" t="n">
-        <v>2</v>
+        <v>10982.17</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>3.57</v>
+        <v>17973.24</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>1785</v>
+        <v>1636.583662427371</v>
       </c>
     </row>
     <row r="102">
@@ -21023,17 +21426,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C102" s="6" t="n">
-        <v>12031.83</v>
+        <v>9981.849999999999</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>14194.2</v>
+        <v>16002.43</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>1179.720790602925</v>
+        <v>1603.152722190777</v>
       </c>
     </row>
     <row r="103">
@@ -21044,17 +21447,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C103" s="6" t="n">
-        <v>0.05</v>
+        <v>2</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>0.24</v>
+        <v>3.57</v>
       </c>
       <c r="E103" s="6" t="n">
-        <v>4800</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="104">
@@ -21065,17 +21468,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>653.25</v>
+        <v>12058.65</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>636.14</v>
+        <v>14333.39</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>973.80788365863</v>
+        <v>1188.639690180908</v>
       </c>
     </row>
     <row r="105">
@@ -21086,17 +21489,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>20116.69</v>
+        <v>0.05</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>18313.92</v>
+        <v>0.24</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>910.3843624373593</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="106">
@@ -21107,17 +21510,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C106" s="6" t="n">
-        <v>637.12</v>
+        <v>676.89</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>972.5999999999999</v>
+        <v>659.0599999999999</v>
       </c>
       <c r="E106" s="6" t="n">
-        <v>1526.557006529382</v>
+        <v>973.6589401527575</v>
       </c>
     </row>
     <row r="107">
@@ -21128,17 +21531,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C107" s="6" t="n">
-        <v>328.9</v>
+        <v>20116.69</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>438.0000000000001</v>
+        <v>18313.92</v>
       </c>
       <c r="E107" s="6" t="n">
-        <v>1331.711766494376</v>
+        <v>910.3843624373593</v>
       </c>
     </row>
     <row r="108">
@@ -21149,17 +21552,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="C108" s="6" t="n">
-        <v>8429.839999999997</v>
+        <v>637.1800000000001</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>21945.02</v>
+        <v>972.8299999999999</v>
       </c>
       <c r="E108" s="6" t="n">
-        <v>2603.254628794853</v>
+        <v>1526.774223924165</v>
       </c>
     </row>
     <row r="109">
@@ -21170,16 +21573,58 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>329.01</v>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>438.59</v>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v>1333.059785416857</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>9509.679999999998</v>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>24837.41000000001</v>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>2611.80292081332</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Structural Steel</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>Vietnam</t>
         </is>
       </c>
-      <c r="C109" s="6" t="n">
+      <c r="C111" s="6" t="n">
         <v>690.49</v>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D111" s="6" t="n">
         <v>579.4100000000001</v>
       </c>
-      <c r="E109" s="6" t="n">
+      <c r="E111" s="6" t="n">
         <v>839.1287346666861</v>
       </c>
     </row>
